--- a/crop_timeline_coverage.xlsx
+++ b/crop_timeline_coverage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687402E9-91E4-F647-B8BC-DC593DBE096C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EFF92B-F82E-C04C-9EE5-CB646ABCDDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45780" yWindow="-5020" windowWidth="23440" windowHeight="19500" firstSheet="3" activeTab="14" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
+    <workbookView xWindow="42340" yWindow="-5040" windowWidth="23440" windowHeight="19500" firstSheet="3" activeTab="7" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
   </bookViews>
   <sheets>
     <sheet name="crop_stage" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="858">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="857">
   <si>
     <t>crop_id</t>
   </si>
@@ -2624,9 +2624,6 @@
   </si>
   <si>
     <t>Effective</t>
-  </si>
-  <si>
-    <t>Poor</t>
   </si>
   <si>
     <t>Ineffective</t>
@@ -5450,7 +5447,7 @@
         <v>838</v>
       </c>
       <c r="C17" t="s">
-        <v>845</v>
+        <v>855</v>
       </c>
       <c r="K17" t="s">
         <v>168</v>
@@ -5467,7 +5464,7 @@
         <v>839</v>
       </c>
       <c r="C18" t="s">
-        <v>855</v>
+        <v>844</v>
       </c>
       <c r="K18" t="s">
         <v>169</v>
@@ -5484,7 +5481,7 @@
         <v>840</v>
       </c>
       <c r="C19" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
       <c r="L19" s="1"/>
       <c r="O19" t="s">
@@ -5492,17 +5489,11 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C20" t="s">
-        <v>856</v>
-      </c>
       <c r="O20" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="C21" t="s">
-        <v>857</v>
-      </c>
       <c r="O21" t="s">
         <v>308</v>
       </c>
@@ -11039,7 +11030,7 @@
         <v>769</v>
       </c>
       <c r="G11" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -11064,7 +11055,7 @@
         <v>769</v>
       </c>
       <c r="G12" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -11089,7 +11080,7 @@
         <v>769</v>
       </c>
       <c r="G13" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -11114,7 +11105,7 @@
         <v>769</v>
       </c>
       <c r="G14" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -11139,7 +11130,7 @@
         <v>769</v>
       </c>
       <c r="G15" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -11164,7 +11155,7 @@
         <v>769</v>
       </c>
       <c r="G16" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -11189,7 +11180,7 @@
         <v>769</v>
       </c>
       <c r="G17" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -11214,7 +11205,7 @@
         <v>769</v>
       </c>
       <c r="G18" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -11239,7 +11230,7 @@
         <v>769</v>
       </c>
       <c r="G19" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -11264,7 +11255,7 @@
         <v>769</v>
       </c>
       <c r="G20" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -11486,9 +11477,9 @@
           </x14:formula1>
           <xm:sqref>F2:F28</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AA13F0FC-C711-9348-9AE7-D388B7DC6EB3}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{59D3603E-4EBE-5F44-B8B0-FAA4AF0FC40D}">
           <x14:formula1>
-            <xm:f>ref!$C$17:$C$21</xm:f>
+            <xm:f>ref!$C$17:$C$19</xm:f>
           </x14:formula1>
           <xm:sqref>G2:G28</xm:sqref>
         </x14:dataValidation>
@@ -12026,9 +12017,9 @@
           </x14:formula1>
           <xm:sqref>E2:E14</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{684614DA-054C-2F42-8E88-A67A6EEFACB5}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{35592C18-ECB1-C14B-A4E9-0D58D9131625}">
           <x14:formula1>
-            <xm:f>ref!$C$17:$C$21</xm:f>
+            <xm:f>ref!$C$17:$C$19</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F14</xm:sqref>
         </x14:dataValidation>

--- a/crop_timeline_coverage.xlsx
+++ b/crop_timeline_coverage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pongthanatburanachon/Desktop/work/dashboard/crop_timeline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05EFF92B-F82E-C04C-9EE5-CB646ABCDDA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE5D742-2ADA-4A41-92EE-769650855E15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42340" yWindow="-5040" windowWidth="23440" windowHeight="19500" firstSheet="3" activeTab="7" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
+    <workbookView xWindow="38980" yWindow="-5060" windowWidth="23440" windowHeight="19500" firstSheet="4" activeTab="5" xr2:uid="{BADFB13E-FBB2-E340-984B-DD0D2D768ACB}"/>
   </bookViews>
   <sheets>
     <sheet name="crop_stage" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,8 @@
     <sheet name="prod_fer" sheetId="16" r:id="rId12"/>
     <sheet name="fertilizer" sheetId="8" r:id="rId13"/>
     <sheet name="crop_ref" sheetId="10" r:id="rId14"/>
-    <sheet name="ref" sheetId="9" r:id="rId15"/>
+    <sheet name="price_history" sheetId="17" r:id="rId15"/>
+    <sheet name="ref" sheetId="9" r:id="rId16"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">crop_disease!$A$1:$H$19</definedName>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1863" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2318" uniqueCount="1055">
   <si>
     <t>crop_id</t>
   </si>
@@ -2353,24 +2354,15 @@
     <t>SHK</t>
   </si>
   <si>
-    <t>12%+27%W/V</t>
-  </si>
-  <si>
     <t>EC</t>
   </si>
   <si>
     <t>13+5</t>
   </si>
   <si>
-    <t>72%W/V</t>
-  </si>
-  <si>
     <t>frontier-p</t>
   </si>
   <si>
-    <t>48%W/V</t>
-  </si>
-  <si>
     <t>bramus</t>
   </si>
   <si>
@@ -2386,18 +2378,12 @@
     <t>imidacloprid+lambda-cyhalothrin</t>
   </si>
   <si>
-    <t>16%+12%W/V</t>
-  </si>
-  <si>
     <t>SC</t>
   </si>
   <si>
     <t>4A+3A</t>
   </si>
   <si>
-    <t>50%+5%W/V</t>
-  </si>
-  <si>
     <t>1B+15</t>
   </si>
   <si>
@@ -2416,18 +2402,12 @@
     <t>เทรนนิว</t>
   </si>
   <si>
-    <t>25%W/V</t>
-  </si>
-  <si>
     <t>C11</t>
   </si>
   <si>
     <t>ทานชิ</t>
   </si>
   <si>
-    <t>50%W/V</t>
-  </si>
-  <si>
     <t>B1</t>
   </si>
   <si>
@@ -2437,9 +2417,6 @@
     <t xml:space="preserve">copper sulfate </t>
   </si>
   <si>
-    <t>34.5%W/V</t>
-  </si>
-  <si>
     <t>แบคทรอล</t>
   </si>
   <si>
@@ -2614,12 +2591,6 @@
     <t>price_per_bag</t>
   </si>
   <si>
-    <t>price_per_20l</t>
-  </si>
-  <si>
-    <t>price_per_rai</t>
-  </si>
-  <si>
     <t>efficiency</t>
   </si>
   <si>
@@ -2627,13 +2598,637 @@
   </si>
   <si>
     <t>Ineffective</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propineb+iprovalicarb </t>
+  </si>
+  <si>
+    <t xml:space="preserve">invento </t>
+  </si>
+  <si>
+    <t>M03+40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mancozeb+valifenalate </t>
+  </si>
+  <si>
+    <t>Estocade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mancozeb+mandipropamid </t>
+  </si>
+  <si>
+    <t>REVUS MZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propineb + fluopicolide </t>
+  </si>
+  <si>
+    <t>Trivia</t>
+  </si>
+  <si>
+    <t>M03+43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mancozeb+cymoxanil </t>
+  </si>
+  <si>
+    <t>Curzate</t>
+  </si>
+  <si>
+    <t>M03+27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mancozeb + metalaxyl-M </t>
+  </si>
+  <si>
+    <t>RIDOMIL GOLD</t>
+  </si>
+  <si>
+    <t>M03+4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chlorothalonil+metalaxyl  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOLIO GOLD </t>
+  </si>
+  <si>
+    <t>M05+4</t>
+  </si>
+  <si>
+    <t>Equation</t>
+  </si>
+  <si>
+    <t>27+11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fosetyl-aluminium+fluopicolide </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profiler </t>
+  </si>
+  <si>
+    <t>P07+43</t>
+  </si>
+  <si>
+    <t>Orvego</t>
+  </si>
+  <si>
+    <t>40+45</t>
+  </si>
+  <si>
+    <t>Banjo Forte</t>
+  </si>
+  <si>
+    <t>40+29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dimethomorph + pyraclostrobin </t>
+  </si>
+  <si>
+    <t>Generic Products</t>
+  </si>
+  <si>
+    <t>40+11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dimethomorph + prochloraz </t>
+  </si>
+  <si>
+    <t>เดมี่</t>
+  </si>
+  <si>
+    <t>40+3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">propamocarb + metalaxyl </t>
+  </si>
+  <si>
+    <t>28+4</t>
+  </si>
+  <si>
+    <t>Fluopicolide + Propamocarb hydrochloride</t>
+  </si>
+  <si>
+    <t>พิโคคาร์บ</t>
+  </si>
+  <si>
+    <t>28+43</t>
+  </si>
+  <si>
+    <t>BAYER</t>
+  </si>
+  <si>
+    <t>SOTUS</t>
+  </si>
+  <si>
+    <t>Syngenta</t>
+  </si>
+  <si>
+    <t>CORTEVA</t>
+  </si>
+  <si>
+    <t>CHIATAI</t>
+  </si>
+  <si>
+    <t>BASF</t>
+  </si>
+  <si>
+    <t>ADAMA</t>
+  </si>
+  <si>
+    <t>GLOBAL</t>
+  </si>
+  <si>
+    <t>THEPWATANA</t>
+  </si>
+  <si>
+    <t>RAINBOW</t>
+  </si>
+  <si>
+    <t>61.3%+5.5%</t>
+  </si>
+  <si>
+    <t>40%+4% W/V</t>
+  </si>
+  <si>
+    <t>60%+6%</t>
+  </si>
+  <si>
+    <t>64%+8%</t>
+  </si>
+  <si>
+    <t>66.7%+4.4%</t>
+  </si>
+  <si>
+    <t>Formetanate hydrochioride</t>
+  </si>
+  <si>
+    <t>Dicarzol</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>Benfuracarb</t>
+  </si>
+  <si>
+    <t>oncol</t>
+  </si>
+  <si>
+    <t>Profenofos</t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t>Pirimiphos-methyl</t>
+  </si>
+  <si>
+    <t>Actellic 50EC</t>
+  </si>
+  <si>
+    <t>Fipronil</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>Fenpropathrin</t>
+  </si>
+  <si>
+    <t>ดานิทอล</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>Etofenprox</t>
+  </si>
+  <si>
+    <t>ทรีบอน</t>
+  </si>
+  <si>
+    <t>Thiamethoxam</t>
+  </si>
+  <si>
+    <t>Amphan</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>Alanto</t>
+  </si>
+  <si>
+    <t>Clothianidin</t>
+  </si>
+  <si>
+    <t>แดนท๊อซ</t>
+  </si>
+  <si>
+    <t>Imidacloprid</t>
+  </si>
+  <si>
+    <t>โปรวาโด</t>
+  </si>
+  <si>
+    <t>อิมิดา</t>
+  </si>
+  <si>
+    <t>Acetamiprid</t>
+  </si>
+  <si>
+    <t>Molan</t>
+  </si>
+  <si>
+    <t>Dinotrfuran</t>
+  </si>
+  <si>
+    <t>ไดโนทีฟูแรน</t>
+  </si>
+  <si>
+    <t>Spinosad</t>
+  </si>
+  <si>
+    <t>สปินโนขแซด</t>
+  </si>
+  <si>
+    <t>Spinetiram</t>
+  </si>
+  <si>
+    <t>เอ็กซอล</t>
+  </si>
+  <si>
+    <t>Abamectin</t>
+  </si>
+  <si>
+    <t>แจคเก็ต</t>
+  </si>
+  <si>
+    <t>Pymeteozine</t>
+  </si>
+  <si>
+    <t>9B</t>
+  </si>
+  <si>
+    <t>Diafenthiuron</t>
+  </si>
+  <si>
+    <t>Remotus</t>
+  </si>
+  <si>
+    <t>12A</t>
+  </si>
+  <si>
+    <t>Fionicmamid</t>
+  </si>
+  <si>
+    <t>Teppeki</t>
+  </si>
+  <si>
+    <t>Isocycloseram</t>
+  </si>
+  <si>
+    <t>Simodis</t>
+  </si>
+  <si>
+    <t>Flometoquin</t>
+  </si>
+  <si>
+    <t>Kagura</t>
+  </si>
+  <si>
+    <t>TJC</t>
+  </si>
+  <si>
+    <t>(Generic)</t>
+  </si>
+  <si>
+    <t>Sotus</t>
+  </si>
+  <si>
+    <t>เทพวัฒนา</t>
+  </si>
+  <si>
+    <t>bayer</t>
+  </si>
+  <si>
+    <t>Global Crop</t>
+  </si>
+  <si>
+    <t>UPL</t>
+  </si>
+  <si>
+    <t>sotus</t>
+  </si>
+  <si>
+    <t>Modify Agrocrop</t>
+  </si>
+  <si>
+    <t>SP</t>
+  </si>
+  <si>
+    <t>20% W/V</t>
+  </si>
+  <si>
+    <t>50% W/V</t>
+  </si>
+  <si>
+    <t>25% W/V</t>
+  </si>
+  <si>
+    <t>5% W/V</t>
+  </si>
+  <si>
+    <t>10% W/V</t>
+  </si>
+  <si>
+    <t>35% W/V</t>
+  </si>
+  <si>
+    <t>FS</t>
+  </si>
+  <si>
+    <t>24% W/V</t>
+  </si>
+  <si>
+    <t>SG</t>
+  </si>
+  <si>
+    <t>12% W/V</t>
+  </si>
+  <si>
+    <t>1.8% W/V</t>
+  </si>
+  <si>
+    <t>3.6% W/V</t>
+  </si>
+  <si>
+    <t>EW</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>10.6% W/V</t>
+  </si>
+  <si>
+    <t>16%+12% W/V</t>
+  </si>
+  <si>
+    <t>50%+5% W/V</t>
+  </si>
+  <si>
+    <t>20%</t>
+  </si>
+  <si>
+    <t>16%</t>
+  </si>
+  <si>
+    <t>70%</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>Formular-A connect</t>
+  </si>
+  <si>
+    <t>แมคเซนด์ 25</t>
+  </si>
+  <si>
+    <t>Hexythiazox</t>
+  </si>
+  <si>
+    <t>Nissorun</t>
+  </si>
+  <si>
+    <t>10A</t>
+  </si>
+  <si>
+    <t>Nissozin</t>
+  </si>
+  <si>
+    <t>Fenbutatin oxide</t>
+  </si>
+  <si>
+    <t>Walk</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>Formular-A</t>
+  </si>
+  <si>
+    <t>Propargite</t>
+  </si>
+  <si>
+    <t>12C</t>
+  </si>
+  <si>
+    <t>Omite 30</t>
+  </si>
+  <si>
+    <t>Omite 57EW</t>
+  </si>
+  <si>
+    <t>Amitraz</t>
+  </si>
+  <si>
+    <t>Bifenazate</t>
+  </si>
+  <si>
+    <t>ACRAMITE</t>
+  </si>
+  <si>
+    <t>20D</t>
+  </si>
+  <si>
+    <t>zagro</t>
+  </si>
+  <si>
+    <t>Fenazaquin</t>
+  </si>
+  <si>
+    <t>Totem</t>
+  </si>
+  <si>
+    <t>21A</t>
+  </si>
+  <si>
+    <t>Fenpyroximate</t>
+  </si>
+  <si>
+    <t>Ortus</t>
+  </si>
+  <si>
+    <t>PATO</t>
+  </si>
+  <si>
+    <t>Pyridaben</t>
+  </si>
+  <si>
+    <t>Sanmite</t>
+  </si>
+  <si>
+    <t>UPL(อริสต้า)</t>
+  </si>
+  <si>
+    <t>ไพริดาเบน</t>
+  </si>
+  <si>
+    <t>Tebufenpyrad</t>
+  </si>
+  <si>
+    <t>Kyra</t>
+  </si>
+  <si>
+    <t>Oberon</t>
+  </si>
+  <si>
+    <t>Bayer</t>
+  </si>
+  <si>
+    <t>Spirodiclofen</t>
+  </si>
+  <si>
+    <t>Bangkokinter agriech</t>
+  </si>
+  <si>
+    <t>Cyfiumetofen</t>
+  </si>
+  <si>
+    <t>Danisaraba</t>
+  </si>
+  <si>
+    <t>25A</t>
+  </si>
+  <si>
+    <t>Cyenopyrafen</t>
+  </si>
+  <si>
+    <t>Kunoichi</t>
+  </si>
+  <si>
+    <t>syngenta</t>
+  </si>
+  <si>
+    <t>Pyfiubumide</t>
+  </si>
+  <si>
+    <t>Jatac</t>
+  </si>
+  <si>
+    <t>25B</t>
+  </si>
+  <si>
+    <t>Sulfur</t>
+  </si>
+  <si>
+    <t>Microthiol</t>
+  </si>
+  <si>
+    <t>M 02</t>
+  </si>
+  <si>
+    <t>34.5% W/V</t>
+  </si>
+  <si>
+    <t>66.7%+6%</t>
+  </si>
+  <si>
+    <t>64%+4%</t>
+  </si>
+  <si>
+    <t>60%+5%</t>
+  </si>
+  <si>
+    <t>30%+22.5%</t>
+  </si>
+  <si>
+    <t>22.5%+30% W/V</t>
+  </si>
+  <si>
+    <t>20%+20% W/V</t>
+  </si>
+  <si>
+    <t>12%+6.7%</t>
+  </si>
+  <si>
+    <t>15%+15% W/V</t>
+  </si>
+  <si>
+    <t>10%+15%</t>
+  </si>
+  <si>
+    <t>6.2%+62.5% W/V</t>
+  </si>
+  <si>
+    <t>55% W/V</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>57% W/V</t>
+  </si>
+  <si>
+    <t>48% W/V</t>
+  </si>
+  <si>
+    <t>13.5% W/V</t>
+  </si>
+  <si>
+    <t>36% W/V</t>
+  </si>
+  <si>
+    <t>30% W/V</t>
+  </si>
+  <si>
+    <t>21.4% W/V</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>12%+27% W/V</t>
+  </si>
+  <si>
+    <t>72% W/V</t>
+  </si>
+  <si>
+    <t>snapshot_date</t>
+  </si>
+  <si>
+    <t>product_id</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>Herbicide</t>
+  </si>
+  <si>
+    <t>Insecticide</t>
+  </si>
+  <si>
+    <t>Fungicide</t>
+  </si>
+  <si>
+    <t>lookup_idx</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2661,6 +3256,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF808080"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2679,10 +3296,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2695,9 +3313,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{B8A6BED4-4B8C-F34C-8E60-37D58CC4D80A}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3007,6 +3629,28 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{9EF27160-3A2B-AF41-A94B-C43B708DEADB}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;dff3854a-6998-4263-a1ca-5a3c2b47c625&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B91F3A6-442D-424C-AB27-8C298D5989C1}">
   <sheetPr filterMode="1"/>
@@ -3693,16 +4337,16 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{639ADB74-B9D2-BD48-A768-A8A16773930D}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="16.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="B1" t="s">
         <v>761</v>
@@ -3720,30 +4364,24 @@
         <v>760</v>
       </c>
       <c r="G1" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="H1" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="I1" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="J1" t="s">
-        <v>848</v>
-      </c>
-      <c r="K1" t="s">
-        <v>847</v>
-      </c>
-      <c r="L1" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="B2" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C2" t="s">
         <v>764</v>
@@ -3751,38 +4389,31 @@
       <c r="D2" t="s">
         <v>674</v>
       </c>
-      <c r="E2" t="s">
-        <v>786</v>
+      <c r="E2" s="1" t="s">
+        <v>959</v>
       </c>
       <c r="F2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="H2" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="I2">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>0.1</v>
-      </c>
-      <c r="L2">
-        <f t="shared" ref="L2:L3" si="0">(20*I2)/J2</f>
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="B3" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="C3" t="s">
         <v>764</v>
@@ -3790,109 +4421,583 @@
       <c r="D3" t="s">
         <v>729</v>
       </c>
-      <c r="E3" t="s">
-        <v>789</v>
+      <c r="E3" s="1" t="s">
+        <v>958</v>
       </c>
       <c r="F3" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="H3" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="I3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>0.3</v>
-      </c>
-      <c r="L3">
-        <f t="shared" si="0"/>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="B4" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="C4" t="s">
         <v>764</v>
       </c>
       <c r="D4" t="s">
-        <v>792</v>
-      </c>
-      <c r="E4" t="s">
-        <v>793</v>
+        <v>785</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>1026</v>
       </c>
       <c r="F4" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>193</v>
       </c>
       <c r="H4" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="I4">
-        <v>350</v>
+        <v>5000</v>
       </c>
       <c r="J4">
-        <v>5</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <f>(20*I4)/J4</f>
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="B5" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="C5" t="s">
         <v>764</v>
       </c>
       <c r="D5" t="s">
-        <v>795</v>
-      </c>
-      <c r="E5" t="s">
-        <v>796</v>
+        <v>787</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>788</v>
       </c>
       <c r="F5" t="s">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>798</v>
+        <v>790</v>
       </c>
       <c r="H5" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="I5">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>0.4</v>
-      </c>
-      <c r="L5">
-        <f>(20*I5)/J5</f>
-        <v>13800</v>
-      </c>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>873</v>
+      </c>
+      <c r="C6" t="s">
+        <v>892</v>
+      </c>
+      <c r="D6" t="s">
+        <v>459</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F6" t="s">
+        <v>773</v>
+      </c>
+      <c r="G6" t="s">
+        <v>874</v>
+      </c>
+      <c r="H6" t="s">
+        <v>831</v>
+      </c>
+      <c r="I6">
+        <v>1250</v>
+      </c>
+      <c r="J6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>871</v>
+      </c>
+      <c r="C7" t="s">
+        <v>891</v>
+      </c>
+      <c r="D7" t="s">
+        <v>458</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F7" t="s">
+        <v>773</v>
+      </c>
+      <c r="G7" t="s">
+        <v>872</v>
+      </c>
+      <c r="H7" t="s">
+        <v>830</v>
+      </c>
+      <c r="I7">
+        <v>950</v>
+      </c>
+      <c r="J7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>848</v>
+      </c>
+      <c r="C8" t="s">
+        <v>886</v>
+      </c>
+      <c r="D8" t="s">
+        <v>847</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="F8" t="s">
+        <v>789</v>
+      </c>
+      <c r="G8" t="s">
+        <v>849</v>
+      </c>
+      <c r="H8" t="s">
+        <v>830</v>
+      </c>
+      <c r="I8">
+        <v>620</v>
+      </c>
+      <c r="J8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>855</v>
+      </c>
+      <c r="C9" t="s">
+        <v>886</v>
+      </c>
+      <c r="D9" t="s">
+        <v>854</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F9" t="s">
+        <v>789</v>
+      </c>
+      <c r="G9" t="s">
+        <v>856</v>
+      </c>
+      <c r="H9" t="s">
+        <v>830</v>
+      </c>
+      <c r="I9">
+        <v>800</v>
+      </c>
+      <c r="J9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>869</v>
+      </c>
+      <c r="C10" t="s">
+        <v>890</v>
+      </c>
+      <c r="D10" t="s">
+        <v>868</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="F10" t="s">
+        <v>778</v>
+      </c>
+      <c r="G10" t="s">
+        <v>870</v>
+      </c>
+      <c r="H10" t="s">
+        <v>832</v>
+      </c>
+      <c r="I10">
+        <v>230</v>
+      </c>
+      <c r="J10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>858</v>
+      </c>
+      <c r="C11" t="s">
+        <v>889</v>
+      </c>
+      <c r="D11" t="s">
+        <v>857</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="F11" t="s">
+        <v>778</v>
+      </c>
+      <c r="G11" t="s">
+        <v>859</v>
+      </c>
+      <c r="H11" t="s">
+        <v>831</v>
+      </c>
+      <c r="I11">
+        <v>280</v>
+      </c>
+      <c r="J11">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>866</v>
+      </c>
+      <c r="C12" t="s">
+        <v>889</v>
+      </c>
+      <c r="D12" t="s">
+        <v>425</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F12" t="s">
+        <v>778</v>
+      </c>
+      <c r="G12" t="s">
+        <v>867</v>
+      </c>
+      <c r="H12" t="s">
+        <v>831</v>
+      </c>
+      <c r="I12">
+        <v>2200</v>
+      </c>
+      <c r="J12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>876</v>
+      </c>
+      <c r="C13" t="s">
+        <v>893</v>
+      </c>
+      <c r="D13" t="s">
+        <v>875</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F13" t="s">
+        <v>778</v>
+      </c>
+      <c r="G13" t="s">
+        <v>877</v>
+      </c>
+      <c r="H13" t="s">
+        <v>832</v>
+      </c>
+      <c r="I13">
+        <v>680</v>
+      </c>
+      <c r="J13">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>876</v>
+      </c>
+      <c r="C14" t="s">
+        <v>893</v>
+      </c>
+      <c r="D14" t="s">
+        <v>881</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F14" t="s">
+        <v>789</v>
+      </c>
+      <c r="G14" t="s">
+        <v>882</v>
+      </c>
+      <c r="H14" t="s">
+        <v>832</v>
+      </c>
+      <c r="I14">
+        <v>280</v>
+      </c>
+      <c r="J14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>884</v>
+      </c>
+      <c r="C15" t="s">
+        <v>895</v>
+      </c>
+      <c r="D15" t="s">
+        <v>883</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F15" t="s">
+        <v>773</v>
+      </c>
+      <c r="G15" t="s">
+        <v>885</v>
+      </c>
+      <c r="H15" t="s">
+        <v>832</v>
+      </c>
+      <c r="I15">
+        <v>880</v>
+      </c>
+      <c r="J15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>851</v>
+      </c>
+      <c r="C16" t="s">
+        <v>887</v>
+      </c>
+      <c r="D16" t="s">
+        <v>850</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="F16" t="s">
+        <v>778</v>
+      </c>
+      <c r="G16" t="s">
+        <v>849</v>
+      </c>
+      <c r="H16" t="s">
+        <v>831</v>
+      </c>
+      <c r="I16">
+        <v>850</v>
+      </c>
+      <c r="J16">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>861</v>
+      </c>
+      <c r="C17" t="s">
+        <v>888</v>
+      </c>
+      <c r="D17" t="s">
+        <v>860</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F17" t="s">
+        <v>778</v>
+      </c>
+      <c r="G17" t="s">
+        <v>862</v>
+      </c>
+      <c r="H17" t="s">
+        <v>830</v>
+      </c>
+      <c r="I17">
+        <v>450</v>
+      </c>
+      <c r="J17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>864</v>
+      </c>
+      <c r="C18" t="s">
+        <v>888</v>
+      </c>
+      <c r="D18" t="s">
+        <v>863</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="F18" t="s">
+        <v>773</v>
+      </c>
+      <c r="G18" t="s">
+        <v>865</v>
+      </c>
+      <c r="H18" t="s">
+        <v>830</v>
+      </c>
+      <c r="I18">
+        <v>300</v>
+      </c>
+      <c r="J18">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>853</v>
+      </c>
+      <c r="C19" t="s">
+        <v>888</v>
+      </c>
+      <c r="D19" t="s">
+        <v>852</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F19" t="s">
+        <v>778</v>
+      </c>
+      <c r="G19" t="s">
+        <v>849</v>
+      </c>
+      <c r="H19" t="s">
+        <v>830</v>
+      </c>
+      <c r="J19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>879</v>
+      </c>
+      <c r="C20" t="s">
+        <v>894</v>
+      </c>
+      <c r="D20" t="s">
+        <v>878</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F20" t="s">
+        <v>773</v>
+      </c>
+      <c r="G20" t="s">
+        <v>880</v>
+      </c>
+      <c r="H20" t="s">
+        <v>832</v>
+      </c>
+      <c r="I20">
+        <v>850</v>
+      </c>
+      <c r="J20">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E22" s="1"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E24" s="1"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E27" s="1"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E28" s="1"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E29" s="1"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E30" s="1"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E33" s="1"/>
+    </row>
+    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E34" s="1"/>
+    </row>
+    <row r="35" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E40" s="1"/>
+    </row>
+    <row r="41" spans="5:5" x14ac:dyDescent="0.2">
+      <c r="E41" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -3904,7 +5009,7 @@
           <x14:formula1>
             <xm:f>ref!$A$17:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H5</xm:sqref>
+          <xm:sqref>H2:H41</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3933,13 +5038,13 @@
         <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="E1" t="s">
         <v>761</v>
       </c>
       <c r="F1" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -3958,10 +5063,10 @@
         <v>fun001</v>
       </c>
       <c r="E2" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="F2" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -3980,10 +5085,10 @@
         <v>fun001</v>
       </c>
       <c r="E3" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="F3" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -4002,10 +5107,10 @@
         <v>fun001</v>
       </c>
       <c r="E4" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="F4" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -4024,10 +5129,10 @@
         <v>fun001</v>
       </c>
       <c r="E5" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="F5" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -4046,10 +5151,10 @@
         <v>fun001</v>
       </c>
       <c r="E6" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="F6" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -4068,10 +5173,10 @@
         <v>fun001</v>
       </c>
       <c r="E7" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="F7" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -4090,10 +5195,10 @@
         <v>fun001</v>
       </c>
       <c r="E8" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="F8" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -4112,10 +5217,10 @@
         <v>fun002</v>
       </c>
       <c r="E9" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F9" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -4134,10 +5239,10 @@
         <v>fun002</v>
       </c>
       <c r="E10" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F10" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -4156,10 +5261,10 @@
         <v>fun002</v>
       </c>
       <c r="E11" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F11" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -4178,10 +5283,10 @@
         <v>fun002</v>
       </c>
       <c r="E12" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F12" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -4200,10 +5305,10 @@
         <v>fun002</v>
       </c>
       <c r="E13" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F13" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -4222,10 +5327,10 @@
         <v>fun002</v>
       </c>
       <c r="E14" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F14" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -4244,10 +5349,10 @@
         <v>fun002</v>
       </c>
       <c r="E15" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="F15" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -4266,10 +5371,10 @@
         <v>fun003</v>
       </c>
       <c r="E16" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="F16" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -4288,10 +5393,10 @@
         <v>fun003</v>
       </c>
       <c r="E17" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="F17" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -4310,10 +5415,10 @@
         <v>fun004</v>
       </c>
       <c r="E18" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="F18" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -4332,10 +5437,10 @@
         <v>fun004</v>
       </c>
       <c r="E19" t="s">
-        <v>794</v>
+        <v>786</v>
       </c>
       <c r="F19" t="s">
-        <v>845</v>
+        <v>837</v>
       </c>
     </row>
   </sheetData>
@@ -4367,7 +5472,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>154</v>
@@ -4376,21 +5481,21 @@
         <v>153</v>
       </c>
       <c r="D1" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="E1" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="F1" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="G1" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>155</v>
@@ -4399,7 +5504,7 @@
         <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E2">
         <v>20000</v>
@@ -4414,7 +5519,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>155</v>
@@ -4423,7 +5528,7 @@
         <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E3">
         <v>23000</v>
@@ -4438,7 +5543,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>155</v>
@@ -4447,7 +5552,7 @@
         <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="E4">
         <v>3000</v>
@@ -4462,7 +5567,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>155</v>
@@ -4471,7 +5576,7 @@
         <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E5">
         <v>25000</v>
@@ -4486,7 +5591,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>155</v>
@@ -4495,7 +5600,7 @@
         <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E6">
         <v>24000</v>
@@ -4510,7 +5615,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>156</v>
@@ -4519,7 +5624,7 @@
         <v>157</v>
       </c>
       <c r="D7" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E7">
         <v>24000</v>
@@ -4534,7 +5639,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>158</v>
@@ -4543,7 +5648,7 @@
         <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E8">
         <v>24000</v>
@@ -4558,7 +5663,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>158</v>
@@ -4567,7 +5672,7 @@
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E9">
         <v>24000</v>
@@ -4582,7 +5687,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>158</v>
@@ -4591,7 +5696,7 @@
         <v>159</v>
       </c>
       <c r="D10" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E10">
         <v>24000</v>
@@ -4606,7 +5711,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>160</v>
@@ -4615,7 +5720,7 @@
         <v>161</v>
       </c>
       <c r="D11" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E11">
         <v>24000</v>
@@ -4630,7 +5735,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>162</v>
@@ -4639,7 +5744,7 @@
         <v>163</v>
       </c>
       <c r="D12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E12">
         <v>26000</v>
@@ -4654,7 +5759,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>166</v>
@@ -4663,7 +5768,7 @@
         <v>164</v>
       </c>
       <c r="D13" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E13">
         <v>24000</v>
@@ -4678,7 +5783,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>167</v>
@@ -4687,7 +5792,7 @@
         <v>165</v>
       </c>
       <c r="D14" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E14">
         <v>24000</v>
@@ -4702,7 +5807,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>168</v>
@@ -4711,7 +5816,7 @@
         <v>37</v>
       </c>
       <c r="D15" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E15">
         <v>24000</v>
@@ -4726,7 +5831,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>169</v>
@@ -4735,7 +5840,7 @@
         <v>36</v>
       </c>
       <c r="D16" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="E16">
         <v>24000</v>
@@ -4782,10 +5887,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="C1" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="D1" t="s">
         <v>153</v>
@@ -4808,10 +5913,10 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="C2" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>34</v>
@@ -4834,10 +5939,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="C3" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>34</v>
@@ -4860,10 +5965,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="C4" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>36</v>
@@ -4886,10 +5991,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="C5" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>35</v>
@@ -4913,10 +6018,10 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="C6" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>171</v>
@@ -4940,10 +6045,10 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="C7" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>157</v>
@@ -5064,6 +6169,2748 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C87063-B1C4-A346-912B-998BFFE13FA3}">
+  <dimension ref="A1:J101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="18" style="10" customWidth="1"/>
+    <col min="5" max="5" width="24.1640625" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D1" t="s">
+        <v>761</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>759</v>
+      </c>
+      <c r="G1" t="s">
+        <v>760</v>
+      </c>
+      <c r="H1" t="s">
+        <v>762</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D2" t="str">
+        <f>IF(OR($B2="",$J2=""),"",IFERROR(INDEX(CHOOSE($J2,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B2,CHOOSE($J2,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J2,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>เซนเที่ยม</v>
+      </c>
+      <c r="E2" t="str">
+        <f>IF(OR($B2="",$J2=""),"",IFERROR(INDEX(CHOOSE($J2,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B2,CHOOSE($J2,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J2,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>clomazone+propanil</v>
+      </c>
+      <c r="F2" t="str">
+        <f>IF(OR($B2="",$J2=""),"",IFERROR(INDEX(CHOOSE($J2,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B2,CHOOSE($J2,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J2,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>12%+27% W/V</v>
+      </c>
+      <c r="G2" t="str">
+        <f>IF(OR($B2="",$J2=""),"",IFERROR(INDEX(CHOOSE($J2,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B2,CHOOSE($J2,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J2,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H2" s="6" t="str">
+        <f>IF(OR($B2="",$J2=""),"",IFERROR(INDEX(CHOOSE($J2,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B2,CHOOSE($J2,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J2,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I2" s="6">
+        <v>500</v>
+      </c>
+      <c r="J2" s="8">
+        <f>IFERROR(MATCH($C2,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B3" t="s">
+        <v>800</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D3" t="str">
+        <f>IF(OR($B3="",$J3=""),"",IFERROR(INDEX(CHOOSE($J3,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B3,CHOOSE($J3,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J3,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>frontier-p</v>
+      </c>
+      <c r="E3" t="str">
+        <f>IF(OR($B3="",$J3=""),"",IFERROR(INDEX(CHOOSE($J3,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B3,CHOOSE($J3,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J3,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>dimethenamid-p</v>
+      </c>
+      <c r="F3" t="str">
+        <f>IF(OR($B3="",$J3=""),"",IFERROR(INDEX(CHOOSE($J3,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B3,CHOOSE($J3,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J3,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>72% W/V</v>
+      </c>
+      <c r="G3" t="str">
+        <f>IF(OR($B3="",$J3=""),"",IFERROR(INDEX(CHOOSE($J3,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B3,CHOOSE($J3,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J3,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H3" s="6" t="str">
+        <f>IF(OR($B3="",$J3=""),"",IFERROR(INDEX(CHOOSE($J3,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B3,CHOOSE($J3,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J3,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I3" s="6">
+        <v>600</v>
+      </c>
+      <c r="J3" s="8">
+        <f>IFERROR(MATCH($C3,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A4" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D4" t="str">
+        <f>IF(OR($B4="",$J4=""),"",IFERROR(INDEX(CHOOSE($J4,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B4,CHOOSE($J4,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J4,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>bramus</v>
+      </c>
+      <c r="E4" t="str">
+        <f>IF(OR($B4="",$J4=""),"",IFERROR(INDEX(CHOOSE($J4,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B4,CHOOSE($J4,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J4,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>bentazone</v>
+      </c>
+      <c r="F4" t="str">
+        <f>IF(OR($B4="",$J4=""),"",IFERROR(INDEX(CHOOSE($J4,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B4,CHOOSE($J4,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J4,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>48% W/V</v>
+      </c>
+      <c r="G4" t="str">
+        <f>IF(OR($B4="",$J4=""),"",IFERROR(INDEX(CHOOSE($J4,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B4,CHOOSE($J4,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J4,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H4" s="6" t="str">
+        <f>IF(OR($B4="",$J4=""),"",IFERROR(INDEX(CHOOSE($J4,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B4,CHOOSE($J4,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J4,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I4" s="6">
+        <v>900</v>
+      </c>
+      <c r="J4" s="8">
+        <f>IFERROR(MATCH($C4,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D5" t="str">
+        <f>IF(OR($B5="",$J5=""),"",IFERROR(INDEX(CHOOSE($J5,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B5,CHOOSE($J5,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J5,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>คิวเทอร์</v>
+      </c>
+      <c r="E5" t="str">
+        <f>IF(OR($B5="",$J5=""),"",IFERROR(INDEX(CHOOSE($J5,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B5,CHOOSE($J5,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J5,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>imidacloprid+lambda-cyhalothrin</v>
+      </c>
+      <c r="F5" t="str">
+        <f>IF(OR($B5="",$J5=""),"",IFERROR(INDEX(CHOOSE($J5,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B5,CHOOSE($J5,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J5,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>16%+12% W/V</v>
+      </c>
+      <c r="G5" t="str">
+        <f>IF(OR($B5="",$J5=""),"",IFERROR(INDEX(CHOOSE($J5,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B5,CHOOSE($J5,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J5,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SC</v>
+      </c>
+      <c r="H5" s="6" t="str">
+        <f>IF(OR($B5="",$J5=""),"",IFERROR(INDEX(CHOOSE($J5,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B5,CHOOSE($J5,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J5,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I5" s="6">
+        <v>590</v>
+      </c>
+      <c r="J5" s="8">
+        <f>IFERROR(MATCH($C5,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B6" t="s">
+        <v>805</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D6" t="str">
+        <f>IF(OR($B6="",$J6=""),"",IFERROR(INDEX(CHOOSE($J6,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B6,CHOOSE($J6,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J6,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>โดรนพลัส</v>
+      </c>
+      <c r="E6" t="str">
+        <f>IF(OR($B6="",$J6=""),"",IFERROR(INDEX(CHOOSE($J6,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B6,CHOOSE($J6,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J6,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>profenofos+lufenuron</v>
+      </c>
+      <c r="F6" t="str">
+        <f>IF(OR($B6="",$J6=""),"",IFERROR(INDEX(CHOOSE($J6,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B6,CHOOSE($J6,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J6,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>50%+5% W/V</v>
+      </c>
+      <c r="G6" t="str">
+        <f>IF(OR($B6="",$J6=""),"",IFERROR(INDEX(CHOOSE($J6,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B6,CHOOSE($J6,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J6,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H6" s="6" t="str">
+        <f>IF(OR($B6="",$J6=""),"",IFERROR(INDEX(CHOOSE($J6,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B6,CHOOSE($J6,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J6,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I6" s="6">
+        <v>590</v>
+      </c>
+      <c r="J6" s="8">
+        <f>IFERROR(MATCH($C6,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B7" t="s">
+        <v>806</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D7" t="str">
+        <f>IF(OR($B7="",$J7=""),"",IFERROR(INDEX(CHOOSE($J7,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B7,CHOOSE($J7,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J7,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>ออสเรียม</v>
+      </c>
+      <c r="E7" t="str">
+        <f>IF(OR($B7="",$J7=""),"",IFERROR(INDEX(CHOOSE($J7,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B7,CHOOSE($J7,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J7,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>emamectin benzoate+lufenuron</v>
+      </c>
+      <c r="F7" t="str">
+        <f>IF(OR($B7="",$J7=""),"",IFERROR(INDEX(CHOOSE($J7,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B7,CHOOSE($J7,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J7,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>10%+40%</v>
+      </c>
+      <c r="G7" t="str">
+        <f>IF(OR($B7="",$J7=""),"",IFERROR(INDEX(CHOOSE($J7,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B7,CHOOSE($J7,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J7,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>WG</v>
+      </c>
+      <c r="H7" s="6" t="str">
+        <f>IF(OR($B7="",$J7=""),"",IFERROR(INDEX(CHOOSE($J7,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B7,CHOOSE($J7,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J7,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I7" s="6">
+        <v>40</v>
+      </c>
+      <c r="J7" s="8">
+        <f>IFERROR(MATCH($C7,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B8" t="s">
+        <v>807</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D8" t="str">
+        <f>IF(OR($B8="",$J8=""),"",IFERROR(INDEX(CHOOSE($J8,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B8,CHOOSE($J8,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J8,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>เทรนนิว</v>
+      </c>
+      <c r="E8" t="str">
+        <f>IF(OR($B8="",$J8=""),"",IFERROR(INDEX(CHOOSE($J8,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B8,CHOOSE($J8,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J8,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>pyraclostrobin</v>
+      </c>
+      <c r="F8" t="str">
+        <f>IF(OR($B8="",$J8=""),"",IFERROR(INDEX(CHOOSE($J8,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B8,CHOOSE($J8,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J8,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>25% W/V</v>
+      </c>
+      <c r="G8" t="str">
+        <f>IF(OR($B8="",$J8=""),"",IFERROR(INDEX(CHOOSE($J8,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B8,CHOOSE($J8,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J8,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H8" s="6" t="str">
+        <f>IF(OR($B8="",$J8=""),"",IFERROR(INDEX(CHOOSE($J8,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B8,CHOOSE($J8,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J8,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I8" s="6">
+        <v>590</v>
+      </c>
+      <c r="J8" s="8">
+        <f>IFERROR(MATCH($C8,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B9" t="s">
+        <v>808</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D9" t="str">
+        <f>IF(OR($B9="",$J9=""),"",IFERROR(INDEX(CHOOSE($J9,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B9,CHOOSE($J9,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J9,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>ทานชิ</v>
+      </c>
+      <c r="E9" t="str">
+        <f>IF(OR($B9="",$J9=""),"",IFERROR(INDEX(CHOOSE($J9,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B9,CHOOSE($J9,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J9,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>thiophanate-methyl</v>
+      </c>
+      <c r="F9" t="str">
+        <f>IF(OR($B9="",$J9=""),"",IFERROR(INDEX(CHOOSE($J9,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B9,CHOOSE($J9,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J9,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>50% W/V</v>
+      </c>
+      <c r="G9" t="str">
+        <f>IF(OR($B9="",$J9=""),"",IFERROR(INDEX(CHOOSE($J9,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B9,CHOOSE($J9,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J9,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SC</v>
+      </c>
+      <c r="H9" s="6" t="str">
+        <f>IF(OR($B9="",$J9=""),"",IFERROR(INDEX(CHOOSE($J9,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B9,CHOOSE($J9,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J9,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I9" s="6">
+        <v>600</v>
+      </c>
+      <c r="J9" s="8">
+        <f>IFERROR(MATCH($C9,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B10" t="s">
+        <v>809</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D10" t="str">
+        <f>IF(OR($B10="",$J10=""),"",IFERROR(INDEX(CHOOSE($J10,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B10,CHOOSE($J10,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J10,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>ไตร-เบส บลู</v>
+      </c>
+      <c r="E10" t="str">
+        <f>IF(OR($B10="",$J10=""),"",IFERROR(INDEX(CHOOSE($J10,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B10,CHOOSE($J10,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J10,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v xml:space="preserve">copper sulfate </v>
+      </c>
+      <c r="F10" t="str">
+        <f>IF(OR($B10="",$J10=""),"",IFERROR(INDEX(CHOOSE($J10,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B10,CHOOSE($J10,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J10,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>34.5% W/V</v>
+      </c>
+      <c r="G10" t="str">
+        <f>IF(OR($B10="",$J10=""),"",IFERROR(INDEX(CHOOSE($J10,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B10,CHOOSE($J10,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J10,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SC</v>
+      </c>
+      <c r="H10" s="6" t="str">
+        <f>IF(OR($B10="",$J10=""),"",IFERROR(INDEX(CHOOSE($J10,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B10,CHOOSE($J10,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J10,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I10" s="6">
+        <v>350</v>
+      </c>
+      <c r="J10" s="8">
+        <f>IFERROR(MATCH($C10,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="10">
+        <v>45881</v>
+      </c>
+      <c r="B11" t="s">
+        <v>810</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D11" t="str">
+        <f>IF(OR($B11="",$J11=""),"",IFERROR(INDEX(CHOOSE($J11,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B11,CHOOSE($J11,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J11,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>แบคทรอล</v>
+      </c>
+      <c r="E11" t="str">
+        <f>IF(OR($B11="",$J11=""),"",IFERROR(INDEX(CHOOSE($J11,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B11,CHOOSE($J11,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J11,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>gentamicin sulfate+oxytetracyclin hydrochloride</v>
+      </c>
+      <c r="F11" t="str">
+        <f>IF(OR($B11="",$J11=""),"",IFERROR(INDEX(CHOOSE($J11,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B11,CHOOSE($J11,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J11,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>2%+6%</v>
+      </c>
+      <c r="G11" t="str">
+        <f>IF(OR($B11="",$J11=""),"",IFERROR(INDEX(CHOOSE($J11,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B11,CHOOSE($J11,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J11,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>WP</v>
+      </c>
+      <c r="H11" s="6" t="str">
+        <f>IF(OR($B11="",$J11=""),"",IFERROR(INDEX(CHOOSE($J11,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B11,CHOOSE($J11,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J11,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I11" s="6">
+        <v>690</v>
+      </c>
+      <c r="J11" s="8">
+        <f>IFERROR(MATCH($C11,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B12" t="s">
+        <v>799</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D12" t="str">
+        <f>IF(OR($B12="",$J12=""),"",IFERROR(INDEX(CHOOSE($J12,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B12,CHOOSE($J12,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J12,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>เซนเที่ยม</v>
+      </c>
+      <c r="E12" t="str">
+        <f>IF(OR($B12="",$J12=""),"",IFERROR(INDEX(CHOOSE($J12,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B12,CHOOSE($J12,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J12,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>clomazone+propanil</v>
+      </c>
+      <c r="F12" t="str">
+        <f>IF(OR($B12="",$J12=""),"",IFERROR(INDEX(CHOOSE($J12,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B12,CHOOSE($J12,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J12,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>12%+27% W/V</v>
+      </c>
+      <c r="G12" t="str">
+        <f>IF(OR($B12="",$J12=""),"",IFERROR(INDEX(CHOOSE($J12,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B12,CHOOSE($J12,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J12,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H12" s="6" t="str">
+        <f>IF(OR($B12="",$J12=""),"",IFERROR(INDEX(CHOOSE($J12,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B12,CHOOSE($J12,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J12,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I12" s="6">
+        <v>480</v>
+      </c>
+      <c r="J12" s="8">
+        <f>IFERROR(MATCH($C12,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B13" t="s">
+        <v>800</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D13" t="str">
+        <f>IF(OR($B13="",$J13=""),"",IFERROR(INDEX(CHOOSE($J13,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B13,CHOOSE($J13,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J13,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>frontier-p</v>
+      </c>
+      <c r="E13" t="str">
+        <f>IF(OR($B13="",$J13=""),"",IFERROR(INDEX(CHOOSE($J13,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B13,CHOOSE($J13,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J13,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>dimethenamid-p</v>
+      </c>
+      <c r="F13" t="str">
+        <f>IF(OR($B13="",$J13=""),"",IFERROR(INDEX(CHOOSE($J13,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B13,CHOOSE($J13,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J13,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>72% W/V</v>
+      </c>
+      <c r="G13" t="str">
+        <f>IF(OR($B13="",$J13=""),"",IFERROR(INDEX(CHOOSE($J13,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B13,CHOOSE($J13,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J13,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H13" s="6" t="str">
+        <f>IF(OR($B13="",$J13=""),"",IFERROR(INDEX(CHOOSE($J13,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B13,CHOOSE($J13,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J13,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I13" s="6">
+        <v>620</v>
+      </c>
+      <c r="J13" s="8">
+        <f>IFERROR(MATCH($C13,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A14" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B14" t="s">
+        <v>801</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D14" t="str">
+        <f>IF(OR($B14="",$J14=""),"",IFERROR(INDEX(CHOOSE($J14,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B14,CHOOSE($J14,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J14,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>bramus</v>
+      </c>
+      <c r="E14" t="str">
+        <f>IF(OR($B14="",$J14=""),"",IFERROR(INDEX(CHOOSE($J14,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B14,CHOOSE($J14,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J14,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>bentazone</v>
+      </c>
+      <c r="F14" t="str">
+        <f>IF(OR($B14="",$J14=""),"",IFERROR(INDEX(CHOOSE($J14,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B14,CHOOSE($J14,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J14,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>48% W/V</v>
+      </c>
+      <c r="G14" t="str">
+        <f>IF(OR($B14="",$J14=""),"",IFERROR(INDEX(CHOOSE($J14,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B14,CHOOSE($J14,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J14,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H14" s="6" t="str">
+        <f>IF(OR($B14="",$J14=""),"",IFERROR(INDEX(CHOOSE($J14,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B14,CHOOSE($J14,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J14,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I14" s="6">
+        <v>900</v>
+      </c>
+      <c r="J14" s="8">
+        <f>IFERROR(MATCH($C14,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B15" t="s">
+        <v>804</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D15" t="str">
+        <f>IF(OR($B15="",$J15=""),"",IFERROR(INDEX(CHOOSE($J15,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B15,CHOOSE($J15,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J15,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>คิวเทอร์</v>
+      </c>
+      <c r="E15" t="str">
+        <f>IF(OR($B15="",$J15=""),"",IFERROR(INDEX(CHOOSE($J15,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B15,CHOOSE($J15,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J15,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>imidacloprid+lambda-cyhalothrin</v>
+      </c>
+      <c r="F15" t="str">
+        <f>IF(OR($B15="",$J15=""),"",IFERROR(INDEX(CHOOSE($J15,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B15,CHOOSE($J15,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J15,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>16%+12% W/V</v>
+      </c>
+      <c r="G15" t="str">
+        <f>IF(OR($B15="",$J15=""),"",IFERROR(INDEX(CHOOSE($J15,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B15,CHOOSE($J15,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J15,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SC</v>
+      </c>
+      <c r="H15" s="6" t="str">
+        <f>IF(OR($B15="",$J15=""),"",IFERROR(INDEX(CHOOSE($J15,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B15,CHOOSE($J15,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J15,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I15" s="6">
+        <v>550</v>
+      </c>
+      <c r="J15" s="8">
+        <f>IFERROR(MATCH($C15,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B16" t="s">
+        <v>805</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D16" t="str">
+        <f>IF(OR($B16="",$J16=""),"",IFERROR(INDEX(CHOOSE($J16,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B16,CHOOSE($J16,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J16,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>โดรนพลัส</v>
+      </c>
+      <c r="E16" t="str">
+        <f>IF(OR($B16="",$J16=""),"",IFERROR(INDEX(CHOOSE($J16,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B16,CHOOSE($J16,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J16,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>profenofos+lufenuron</v>
+      </c>
+      <c r="F16" t="str">
+        <f>IF(OR($B16="",$J16=""),"",IFERROR(INDEX(CHOOSE($J16,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B16,CHOOSE($J16,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J16,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>50%+5% W/V</v>
+      </c>
+      <c r="G16" t="str">
+        <f>IF(OR($B16="",$J16=""),"",IFERROR(INDEX(CHOOSE($J16,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B16,CHOOSE($J16,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J16,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H16" s="6" t="str">
+        <f>IF(OR($B16="",$J16=""),"",IFERROR(INDEX(CHOOSE($J16,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B16,CHOOSE($J16,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J16,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I16" s="6">
+        <v>590</v>
+      </c>
+      <c r="J16" s="8">
+        <f>IFERROR(MATCH($C16,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B17" t="s">
+        <v>806</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D17" t="str">
+        <f>IF(OR($B17="",$J17=""),"",IFERROR(INDEX(CHOOSE($J17,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B17,CHOOSE($J17,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J17,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>ออสเรียม</v>
+      </c>
+      <c r="E17" t="str">
+        <f>IF(OR($B17="",$J17=""),"",IFERROR(INDEX(CHOOSE($J17,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B17,CHOOSE($J17,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J17,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>emamectin benzoate+lufenuron</v>
+      </c>
+      <c r="F17" t="str">
+        <f>IF(OR($B17="",$J17=""),"",IFERROR(INDEX(CHOOSE($J17,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B17,CHOOSE($J17,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J17,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>10%+40%</v>
+      </c>
+      <c r="G17" t="str">
+        <f>IF(OR($B17="",$J17=""),"",IFERROR(INDEX(CHOOSE($J17,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B17,CHOOSE($J17,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J17,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>WG</v>
+      </c>
+      <c r="H17" s="6" t="str">
+        <f>IF(OR($B17="",$J17=""),"",IFERROR(INDEX(CHOOSE($J17,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B17,CHOOSE($J17,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J17,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I17" s="6">
+        <v>40</v>
+      </c>
+      <c r="J17" s="8">
+        <f>IFERROR(MATCH($C17,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B18" t="s">
+        <v>807</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D18" t="str">
+        <f>IF(OR($B18="",$J18=""),"",IFERROR(INDEX(CHOOSE($J18,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B18,CHOOSE($J18,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J18,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>เทรนนิว</v>
+      </c>
+      <c r="E18" t="str">
+        <f>IF(OR($B18="",$J18=""),"",IFERROR(INDEX(CHOOSE($J18,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B18,CHOOSE($J18,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J18,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>pyraclostrobin</v>
+      </c>
+      <c r="F18" t="str">
+        <f>IF(OR($B18="",$J18=""),"",IFERROR(INDEX(CHOOSE($J18,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B18,CHOOSE($J18,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J18,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>25% W/V</v>
+      </c>
+      <c r="G18" t="str">
+        <f>IF(OR($B18="",$J18=""),"",IFERROR(INDEX(CHOOSE($J18,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B18,CHOOSE($J18,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J18,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>EC</v>
+      </c>
+      <c r="H18" s="6" t="str">
+        <f>IF(OR($B18="",$J18=""),"",IFERROR(INDEX(CHOOSE($J18,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B18,CHOOSE($J18,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J18,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I18" s="6">
+        <v>550</v>
+      </c>
+      <c r="J18" s="8">
+        <f>IFERROR(MATCH($C18,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B19" t="s">
+        <v>808</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D19" t="str">
+        <f>IF(OR($B19="",$J19=""),"",IFERROR(INDEX(CHOOSE($J19,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B19,CHOOSE($J19,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J19,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>ทานชิ</v>
+      </c>
+      <c r="E19" t="str">
+        <f>IF(OR($B19="",$J19=""),"",IFERROR(INDEX(CHOOSE($J19,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B19,CHOOSE($J19,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J19,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>thiophanate-methyl</v>
+      </c>
+      <c r="F19" t="str">
+        <f>IF(OR($B19="",$J19=""),"",IFERROR(INDEX(CHOOSE($J19,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B19,CHOOSE($J19,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J19,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>50% W/V</v>
+      </c>
+      <c r="G19" t="str">
+        <f>IF(OR($B19="",$J19=""),"",IFERROR(INDEX(CHOOSE($J19,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B19,CHOOSE($J19,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J19,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SC</v>
+      </c>
+      <c r="H19" s="6" t="str">
+        <f>IF(OR($B19="",$J19=""),"",IFERROR(INDEX(CHOOSE($J19,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B19,CHOOSE($J19,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J19,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I19" s="6">
+        <v>580</v>
+      </c>
+      <c r="J19" s="8">
+        <f>IFERROR(MATCH($C19,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B20" t="s">
+        <v>809</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D20" t="str">
+        <f>IF(OR($B20="",$J20=""),"",IFERROR(INDEX(CHOOSE($J20,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B20,CHOOSE($J20,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J20,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>ไตร-เบส บลู</v>
+      </c>
+      <c r="E20" t="str">
+        <f>IF(OR($B20="",$J20=""),"",IFERROR(INDEX(CHOOSE($J20,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B20,CHOOSE($J20,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J20,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v xml:space="preserve">copper sulfate </v>
+      </c>
+      <c r="F20" t="str">
+        <f>IF(OR($B20="",$J20=""),"",IFERROR(INDEX(CHOOSE($J20,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B20,CHOOSE($J20,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J20,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>34.5% W/V</v>
+      </c>
+      <c r="G20" t="str">
+        <f>IF(OR($B20="",$J20=""),"",IFERROR(INDEX(CHOOSE($J20,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B20,CHOOSE($J20,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J20,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SC</v>
+      </c>
+      <c r="H20" s="6" t="str">
+        <f>IF(OR($B20="",$J20=""),"",IFERROR(INDEX(CHOOSE($J20,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B20,CHOOSE($J20,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J20,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I20" s="6">
+        <v>350</v>
+      </c>
+      <c r="J20">
+        <f>IFERROR(MATCH($C20,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" s="10">
+        <v>46271</v>
+      </c>
+      <c r="B21" t="s">
+        <v>810</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D21" t="str">
+        <f>IF(OR($B21="",$J21=""),"",IFERROR(INDEX(CHOOSE($J21,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B21,CHOOSE($J21,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J21,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>แบคทรอล</v>
+      </c>
+      <c r="E21" t="str">
+        <f>IF(OR($B21="",$J21=""),"",IFERROR(INDEX(CHOOSE($J21,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B21,CHOOSE($J21,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J21,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>gentamicin sulfate+oxytetracyclin hydrochloride</v>
+      </c>
+      <c r="F21" t="str">
+        <f>IF(OR($B21="",$J21=""),"",IFERROR(INDEX(CHOOSE($J21,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B21,CHOOSE($J21,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J21,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>2%+6%</v>
+      </c>
+      <c r="G21" t="str">
+        <f>IF(OR($B21="",$J21=""),"",IFERROR(INDEX(CHOOSE($J21,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B21,CHOOSE($J21,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J21,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>WP</v>
+      </c>
+      <c r="H21" s="6" t="str">
+        <f>IF(OR($B21="",$J21=""),"",IFERROR(INDEX(CHOOSE($J21,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B21,CHOOSE($J21,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(H$1,CHOOSE($J21,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v>SHK</v>
+      </c>
+      <c r="I21" s="6">
+        <v>700</v>
+      </c>
+      <c r="J21">
+        <f>IFERROR(MATCH($C21,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D22" t="str">
+        <f>IF(OR($B22="",$J22=""),"",IFERROR(INDEX(CHOOSE($J22,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B22,CHOOSE($J22,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J22,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <f>IF(OR($B22="",$J22=""),"",IFERROR(INDEX(CHOOSE($J22,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B22,CHOOSE($J22,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J22,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <f>IF(OR($B22="",$J22=""),"",IFERROR(INDEX(CHOOSE($J22,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B22,CHOOSE($J22,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J22,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <f>IF(OR($B22="",$J22=""),"",IFERROR(INDEX(CHOOSE($J22,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B22,CHOOSE($J22,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J22,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" t="str">
+        <f>IFERROR(MATCH($C22,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D23" t="str">
+        <f>IF(OR($B23="",$J23=""),"",IFERROR(INDEX(CHOOSE($J23,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B23,CHOOSE($J23,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J23,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <f>IF(OR($B23="",$J23=""),"",IFERROR(INDEX(CHOOSE($J23,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B23,CHOOSE($J23,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J23,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <f>IF(OR($B23="",$J23=""),"",IFERROR(INDEX(CHOOSE($J23,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B23,CHOOSE($J23,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J23,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <f>IF(OR($B23="",$J23=""),"",IFERROR(INDEX(CHOOSE($J23,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B23,CHOOSE($J23,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J23,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" t="str">
+        <f>IFERROR(MATCH($C23,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D24" t="str">
+        <f>IF(OR($B24="",$J24=""),"",IFERROR(INDEX(CHOOSE($J24,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B24,CHOOSE($J24,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J24,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <f>IF(OR($B24="",$J24=""),"",IFERROR(INDEX(CHOOSE($J24,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B24,CHOOSE($J24,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J24,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <f>IF(OR($B24="",$J24=""),"",IFERROR(INDEX(CHOOSE($J24,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B24,CHOOSE($J24,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J24,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <f>IF(OR($B24="",$J24=""),"",IFERROR(INDEX(CHOOSE($J24,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B24,CHOOSE($J24,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J24,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" t="str">
+        <f>IFERROR(MATCH($C24,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D25" t="str">
+        <f>IF(OR($B25="",$J25=""),"",IFERROR(INDEX(CHOOSE($J25,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B25,CHOOSE($J25,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J25,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <f>IF(OR($B25="",$J25=""),"",IFERROR(INDEX(CHOOSE($J25,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B25,CHOOSE($J25,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J25,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <f>IF(OR($B25="",$J25=""),"",IFERROR(INDEX(CHOOSE($J25,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B25,CHOOSE($J25,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J25,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <f>IF(OR($B25="",$J25=""),"",IFERROR(INDEX(CHOOSE($J25,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B25,CHOOSE($J25,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J25,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" t="str">
+        <f>IFERROR(MATCH($C25,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D26" t="str">
+        <f>IF(OR($B26="",$J26=""),"",IFERROR(INDEX(CHOOSE($J26,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B26,CHOOSE($J26,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J26,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <f>IF(OR($B26="",$J26=""),"",IFERROR(INDEX(CHOOSE($J26,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B26,CHOOSE($J26,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J26,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <f>IF(OR($B26="",$J26=""),"",IFERROR(INDEX(CHOOSE($J26,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B26,CHOOSE($J26,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J26,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <f>IF(OR($B26="",$J26=""),"",IFERROR(INDEX(CHOOSE($J26,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B26,CHOOSE($J26,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J26,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" t="str">
+        <f>IFERROR(MATCH($C26,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D27" t="str">
+        <f>IF(OR($B27="",$J27=""),"",IFERROR(INDEX(CHOOSE($J27,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B27,CHOOSE($J27,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J27,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <f>IF(OR($B27="",$J27=""),"",IFERROR(INDEX(CHOOSE($J27,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B27,CHOOSE($J27,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J27,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <f>IF(OR($B27="",$J27=""),"",IFERROR(INDEX(CHOOSE($J27,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B27,CHOOSE($J27,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J27,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <f>IF(OR($B27="",$J27=""),"",IFERROR(INDEX(CHOOSE($J27,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B27,CHOOSE($J27,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J27,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" t="str">
+        <f>IFERROR(MATCH($C27,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D28" t="str">
+        <f>IF(OR($B28="",$J28=""),"",IFERROR(INDEX(CHOOSE($J28,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B28,CHOOSE($J28,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J28,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <f>IF(OR($B28="",$J28=""),"",IFERROR(INDEX(CHOOSE($J28,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B28,CHOOSE($J28,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J28,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <f>IF(OR($B28="",$J28=""),"",IFERROR(INDEX(CHOOSE($J28,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B28,CHOOSE($J28,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J28,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <f>IF(OR($B28="",$J28=""),"",IFERROR(INDEX(CHOOSE($J28,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B28,CHOOSE($J28,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J28,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" t="str">
+        <f>IFERROR(MATCH($C28,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D29" t="str">
+        <f>IF(OR($B29="",$J29=""),"",IFERROR(INDEX(CHOOSE($J29,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B29,CHOOSE($J29,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J29,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <f>IF(OR($B29="",$J29=""),"",IFERROR(INDEX(CHOOSE($J29,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B29,CHOOSE($J29,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J29,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <f>IF(OR($B29="",$J29=""),"",IFERROR(INDEX(CHOOSE($J29,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B29,CHOOSE($J29,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J29,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <f>IF(OR($B29="",$J29=""),"",IFERROR(INDEX(CHOOSE($J29,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B29,CHOOSE($J29,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J29,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" t="str">
+        <f>IFERROR(MATCH($C29,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D30" t="str">
+        <f>IF(OR($B30="",$J30=""),"",IFERROR(INDEX(CHOOSE($J30,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B30,CHOOSE($J30,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J30,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <f>IF(OR($B30="",$J30=""),"",IFERROR(INDEX(CHOOSE($J30,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B30,CHOOSE($J30,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J30,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <f>IF(OR($B30="",$J30=""),"",IFERROR(INDEX(CHOOSE($J30,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B30,CHOOSE($J30,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J30,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <f>IF(OR($B30="",$J30=""),"",IFERROR(INDEX(CHOOSE($J30,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B30,CHOOSE($J30,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J30,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" t="str">
+        <f>IFERROR(MATCH($C30,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D31" t="str">
+        <f>IF(OR($B31="",$J31=""),"",IFERROR(INDEX(CHOOSE($J31,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B31,CHOOSE($J31,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J31,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <f>IF(OR($B31="",$J31=""),"",IFERROR(INDEX(CHOOSE($J31,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B31,CHOOSE($J31,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J31,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <f>IF(OR($B31="",$J31=""),"",IFERROR(INDEX(CHOOSE($J31,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B31,CHOOSE($J31,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J31,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <f>IF(OR($B31="",$J31=""),"",IFERROR(INDEX(CHOOSE($J31,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B31,CHOOSE($J31,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J31,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" t="str">
+        <f>IFERROR(MATCH($C31,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="D32" t="str">
+        <f>IF(OR($B32="",$J32=""),"",IFERROR(INDEX(CHOOSE($J32,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B32,CHOOSE($J32,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J32,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <f>IF(OR($B32="",$J32=""),"",IFERROR(INDEX(CHOOSE($J32,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B32,CHOOSE($J32,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J32,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <f>IF(OR($B32="",$J32=""),"",IFERROR(INDEX(CHOOSE($J32,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B32,CHOOSE($J32,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J32,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <f>IF(OR($B32="",$J32=""),"",IFERROR(INDEX(CHOOSE($J32,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B32,CHOOSE($J32,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J32,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" t="str">
+        <f>IFERROR(MATCH($C32,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D33" t="str">
+        <f>IF(OR($B33="",$J33=""),"",IFERROR(INDEX(CHOOSE($J33,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B33,CHOOSE($J33,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J33,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <f>IF(OR($B33="",$J33=""),"",IFERROR(INDEX(CHOOSE($J33,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B33,CHOOSE($J33,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J33,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <f>IF(OR($B33="",$J33=""),"",IFERROR(INDEX(CHOOSE($J33,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B33,CHOOSE($J33,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J33,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <f>IF(OR($B33="",$J33=""),"",IFERROR(INDEX(CHOOSE($J33,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B33,CHOOSE($J33,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J33,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" t="str">
+        <f>IFERROR(MATCH($C33,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D34" t="str">
+        <f>IF(OR($B34="",$J34=""),"",IFERROR(INDEX(CHOOSE($J34,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B34,CHOOSE($J34,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J34,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <f>IF(OR($B34="",$J34=""),"",IFERROR(INDEX(CHOOSE($J34,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B34,CHOOSE($J34,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J34,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <f>IF(OR($B34="",$J34=""),"",IFERROR(INDEX(CHOOSE($J34,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B34,CHOOSE($J34,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J34,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <f>IF(OR($B34="",$J34=""),"",IFERROR(INDEX(CHOOSE($J34,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B34,CHOOSE($J34,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J34,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" t="str">
+        <f>IFERROR(MATCH($C34,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D35" t="str">
+        <f>IF(OR($B35="",$J35=""),"",IFERROR(INDEX(CHOOSE($J35,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B35,CHOOSE($J35,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J35,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <f>IF(OR($B35="",$J35=""),"",IFERROR(INDEX(CHOOSE($J35,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B35,CHOOSE($J35,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J35,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <f>IF(OR($B35="",$J35=""),"",IFERROR(INDEX(CHOOSE($J35,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B35,CHOOSE($J35,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J35,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <f>IF(OR($B35="",$J35=""),"",IFERROR(INDEX(CHOOSE($J35,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B35,CHOOSE($J35,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J35,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" t="str">
+        <f>IFERROR(MATCH($C35,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D36" t="str">
+        <f>IF(OR($B36="",$J36=""),"",IFERROR(INDEX(CHOOSE($J36,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B36,CHOOSE($J36,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J36,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <f>IF(OR($B36="",$J36=""),"",IFERROR(INDEX(CHOOSE($J36,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B36,CHOOSE($J36,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J36,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <f>IF(OR($B36="",$J36=""),"",IFERROR(INDEX(CHOOSE($J36,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B36,CHOOSE($J36,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J36,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <f>IF(OR($B36="",$J36=""),"",IFERROR(INDEX(CHOOSE($J36,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B36,CHOOSE($J36,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J36,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" t="str">
+        <f>IFERROR(MATCH($C36,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D37" t="str">
+        <f>IF(OR($B37="",$J37=""),"",IFERROR(INDEX(CHOOSE($J37,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B37,CHOOSE($J37,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J37,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <f>IF(OR($B37="",$J37=""),"",IFERROR(INDEX(CHOOSE($J37,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B37,CHOOSE($J37,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J37,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <f>IF(OR($B37="",$J37=""),"",IFERROR(INDEX(CHOOSE($J37,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B37,CHOOSE($J37,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J37,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <f>IF(OR($B37="",$J37=""),"",IFERROR(INDEX(CHOOSE($J37,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B37,CHOOSE($J37,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J37,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" t="str">
+        <f>IFERROR(MATCH($C37,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D38" t="str">
+        <f>IF(OR($B38="",$J38=""),"",IFERROR(INDEX(CHOOSE($J38,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B38,CHOOSE($J38,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J38,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <f>IF(OR($B38="",$J38=""),"",IFERROR(INDEX(CHOOSE($J38,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B38,CHOOSE($J38,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J38,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <f>IF(OR($B38="",$J38=""),"",IFERROR(INDEX(CHOOSE($J38,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B38,CHOOSE($J38,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J38,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <f>IF(OR($B38="",$J38=""),"",IFERROR(INDEX(CHOOSE($J38,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B38,CHOOSE($J38,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J38,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" t="str">
+        <f>IFERROR(MATCH($C38,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D39" t="str">
+        <f>IF(OR($B39="",$J39=""),"",IFERROR(INDEX(CHOOSE($J39,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B39,CHOOSE($J39,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J39,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <f>IF(OR($B39="",$J39=""),"",IFERROR(INDEX(CHOOSE($J39,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B39,CHOOSE($J39,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J39,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <f>IF(OR($B39="",$J39=""),"",IFERROR(INDEX(CHOOSE($J39,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B39,CHOOSE($J39,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J39,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <f>IF(OR($B39="",$J39=""),"",IFERROR(INDEX(CHOOSE($J39,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B39,CHOOSE($J39,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J39,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" t="str">
+        <f>IFERROR(MATCH($C39,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D40" t="str">
+        <f>IF(OR($B40="",$J40=""),"",IFERROR(INDEX(CHOOSE($J40,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B40,CHOOSE($J40,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J40,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <f>IF(OR($B40="",$J40=""),"",IFERROR(INDEX(CHOOSE($J40,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B40,CHOOSE($J40,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J40,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <f>IF(OR($B40="",$J40=""),"",IFERROR(INDEX(CHOOSE($J40,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B40,CHOOSE($J40,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J40,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <f>IF(OR($B40="",$J40=""),"",IFERROR(INDEX(CHOOSE($J40,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B40,CHOOSE($J40,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J40,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H40" s="6"/>
+      <c r="I40" s="6"/>
+      <c r="J40" t="str">
+        <f>IFERROR(MATCH($C40,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D41" t="str">
+        <f>IF(OR($B41="",$J41=""),"",IFERROR(INDEX(CHOOSE($J41,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B41,CHOOSE($J41,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J41,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <f>IF(OR($B41="",$J41=""),"",IFERROR(INDEX(CHOOSE($J41,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B41,CHOOSE($J41,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J41,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <f>IF(OR($B41="",$J41=""),"",IFERROR(INDEX(CHOOSE($J41,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B41,CHOOSE($J41,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J41,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <f>IF(OR($B41="",$J41=""),"",IFERROR(INDEX(CHOOSE($J41,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B41,CHOOSE($J41,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J41,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H41" s="6"/>
+      <c r="I41" s="6"/>
+      <c r="J41" t="str">
+        <f>IFERROR(MATCH($C41,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D42" t="str">
+        <f>IF(OR($B42="",$J42=""),"",IFERROR(INDEX(CHOOSE($J42,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B42,CHOOSE($J42,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J42,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <f>IF(OR($B42="",$J42=""),"",IFERROR(INDEX(CHOOSE($J42,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B42,CHOOSE($J42,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J42,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <f>IF(OR($B42="",$J42=""),"",IFERROR(INDEX(CHOOSE($J42,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B42,CHOOSE($J42,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J42,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <f>IF(OR($B42="",$J42=""),"",IFERROR(INDEX(CHOOSE($J42,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B42,CHOOSE($J42,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J42,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H42" s="6"/>
+      <c r="I42" s="6"/>
+      <c r="J42" t="str">
+        <f>IFERROR(MATCH($C42,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D43" t="str">
+        <f>IF(OR($B43="",$J43=""),"",IFERROR(INDEX(CHOOSE($J43,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B43,CHOOSE($J43,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J43,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <f>IF(OR($B43="",$J43=""),"",IFERROR(INDEX(CHOOSE($J43,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B43,CHOOSE($J43,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J43,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <f>IF(OR($B43="",$J43=""),"",IFERROR(INDEX(CHOOSE($J43,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B43,CHOOSE($J43,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J43,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <f>IF(OR($B43="",$J43=""),"",IFERROR(INDEX(CHOOSE($J43,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B43,CHOOSE($J43,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J43,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
+      <c r="J43" t="str">
+        <f>IFERROR(MATCH($C43,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D44" t="str">
+        <f>IF(OR($B44="",$J44=""),"",IFERROR(INDEX(CHOOSE($J44,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B44,CHOOSE($J44,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J44,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <f>IF(OR($B44="",$J44=""),"",IFERROR(INDEX(CHOOSE($J44,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B44,CHOOSE($J44,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J44,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <f>IF(OR($B44="",$J44=""),"",IFERROR(INDEX(CHOOSE($J44,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B44,CHOOSE($J44,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J44,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <f>IF(OR($B44="",$J44=""),"",IFERROR(INDEX(CHOOSE($J44,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B44,CHOOSE($J44,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J44,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H44" s="6"/>
+      <c r="I44" s="6"/>
+      <c r="J44" t="str">
+        <f>IFERROR(MATCH($C44,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D45" t="str">
+        <f>IF(OR($B45="",$J45=""),"",IFERROR(INDEX(CHOOSE($J45,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B45,CHOOSE($J45,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J45,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E45" t="str">
+        <f>IF(OR($B45="",$J45=""),"",IFERROR(INDEX(CHOOSE($J45,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B45,CHOOSE($J45,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J45,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <f>IF(OR($B45="",$J45=""),"",IFERROR(INDEX(CHOOSE($J45,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B45,CHOOSE($J45,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J45,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G45" t="str">
+        <f>IF(OR($B45="",$J45=""),"",IFERROR(INDEX(CHOOSE($J45,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B45,CHOOSE($J45,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J45,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H45" s="6"/>
+      <c r="I45" s="6"/>
+      <c r="J45" t="str">
+        <f>IFERROR(MATCH($C45,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D46" t="str">
+        <f>IF(OR($B46="",$J46=""),"",IFERROR(INDEX(CHOOSE($J46,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B46,CHOOSE($J46,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J46,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E46" t="str">
+        <f>IF(OR($B46="",$J46=""),"",IFERROR(INDEX(CHOOSE($J46,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B46,CHOOSE($J46,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J46,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <f>IF(OR($B46="",$J46=""),"",IFERROR(INDEX(CHOOSE($J46,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B46,CHOOSE($J46,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J46,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G46" t="str">
+        <f>IF(OR($B46="",$J46=""),"",IFERROR(INDEX(CHOOSE($J46,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B46,CHOOSE($J46,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J46,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H46" s="6"/>
+      <c r="I46" s="6"/>
+      <c r="J46" t="str">
+        <f>IFERROR(MATCH($C46,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D47" t="str">
+        <f>IF(OR($B47="",$J47=""),"",IFERROR(INDEX(CHOOSE($J47,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B47,CHOOSE($J47,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J47,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E47" t="str">
+        <f>IF(OR($B47="",$J47=""),"",IFERROR(INDEX(CHOOSE($J47,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B47,CHOOSE($J47,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J47,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <f>IF(OR($B47="",$J47=""),"",IFERROR(INDEX(CHOOSE($J47,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B47,CHOOSE($J47,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J47,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G47" t="str">
+        <f>IF(OR($B47="",$J47=""),"",IFERROR(INDEX(CHOOSE($J47,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B47,CHOOSE($J47,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J47,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
+      <c r="J47" t="str">
+        <f>IFERROR(MATCH($C47,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D48" t="str">
+        <f>IF(OR($B48="",$J48=""),"",IFERROR(INDEX(CHOOSE($J48,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B48,CHOOSE($J48,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J48,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E48" t="str">
+        <f>IF(OR($B48="",$J48=""),"",IFERROR(INDEX(CHOOSE($J48,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B48,CHOOSE($J48,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J48,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <f>IF(OR($B48="",$J48=""),"",IFERROR(INDEX(CHOOSE($J48,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B48,CHOOSE($J48,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J48,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G48" t="str">
+        <f>IF(OR($B48="",$J48=""),"",IFERROR(INDEX(CHOOSE($J48,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B48,CHOOSE($J48,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J48,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H48" s="6"/>
+      <c r="I48" s="6"/>
+      <c r="J48" t="str">
+        <f>IFERROR(MATCH($C48,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D49" t="str">
+        <f>IF(OR($B49="",$J49=""),"",IFERROR(INDEX(CHOOSE($J49,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B49,CHOOSE($J49,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J49,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E49" t="str">
+        <f>IF(OR($B49="",$J49=""),"",IFERROR(INDEX(CHOOSE($J49,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B49,CHOOSE($J49,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J49,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F49" t="str">
+        <f>IF(OR($B49="",$J49=""),"",IFERROR(INDEX(CHOOSE($J49,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B49,CHOOSE($J49,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J49,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G49" t="str">
+        <f>IF(OR($B49="",$J49=""),"",IFERROR(INDEX(CHOOSE($J49,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B49,CHOOSE($J49,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J49,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H49" s="6"/>
+      <c r="I49" s="6"/>
+      <c r="J49" t="str">
+        <f>IFERROR(MATCH($C49,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D50" t="str">
+        <f>IF(OR($B50="",$J50=""),"",IFERROR(INDEX(CHOOSE($J50,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B50,CHOOSE($J50,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J50,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E50" t="str">
+        <f>IF(OR($B50="",$J50=""),"",IFERROR(INDEX(CHOOSE($J50,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B50,CHOOSE($J50,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J50,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F50" t="str">
+        <f>IF(OR($B50="",$J50=""),"",IFERROR(INDEX(CHOOSE($J50,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B50,CHOOSE($J50,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J50,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <f>IF(OR($B50="",$J50=""),"",IFERROR(INDEX(CHOOSE($J50,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B50,CHOOSE($J50,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J50,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H50" s="6"/>
+      <c r="I50" s="6"/>
+      <c r="J50" t="str">
+        <f>IFERROR(MATCH($C50,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D51" t="str">
+        <f>IF(OR($B51="",$J51=""),"",IFERROR(INDEX(CHOOSE($J51,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B51,CHOOSE($J51,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J51,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E51" t="str">
+        <f>IF(OR($B51="",$J51=""),"",IFERROR(INDEX(CHOOSE($J51,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B51,CHOOSE($J51,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J51,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <f>IF(OR($B51="",$J51=""),"",IFERROR(INDEX(CHOOSE($J51,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B51,CHOOSE($J51,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J51,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G51" t="str">
+        <f>IF(OR($B51="",$J51=""),"",IFERROR(INDEX(CHOOSE($J51,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B51,CHOOSE($J51,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J51,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
+      <c r="J51" t="str">
+        <f>IFERROR(MATCH($C51,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D52" t="str">
+        <f>IF(OR($B52="",$J52=""),"",IFERROR(INDEX(CHOOSE($J52,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B52,CHOOSE($J52,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J52,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E52" t="str">
+        <f>IF(OR($B52="",$J52=""),"",IFERROR(INDEX(CHOOSE($J52,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B52,CHOOSE($J52,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J52,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <f>IF(OR($B52="",$J52=""),"",IFERROR(INDEX(CHOOSE($J52,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B52,CHOOSE($J52,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J52,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G52" t="str">
+        <f>IF(OR($B52="",$J52=""),"",IFERROR(INDEX(CHOOSE($J52,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B52,CHOOSE($J52,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J52,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H52" s="6"/>
+      <c r="I52" s="6"/>
+      <c r="J52" t="str">
+        <f>IFERROR(MATCH($C52,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D53" t="str">
+        <f>IF(OR($B53="",$J53=""),"",IFERROR(INDEX(CHOOSE($J53,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B53,CHOOSE($J53,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J53,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <f>IF(OR($B53="",$J53=""),"",IFERROR(INDEX(CHOOSE($J53,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B53,CHOOSE($J53,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J53,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <f>IF(OR($B53="",$J53=""),"",IFERROR(INDEX(CHOOSE($J53,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B53,CHOOSE($J53,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J53,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G53" t="str">
+        <f>IF(OR($B53="",$J53=""),"",IFERROR(INDEX(CHOOSE($J53,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B53,CHOOSE($J53,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J53,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" t="str">
+        <f>IFERROR(MATCH($C53,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D54" t="str">
+        <f>IF(OR($B54="",$J54=""),"",IFERROR(INDEX(CHOOSE($J54,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B54,CHOOSE($J54,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J54,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <f>IF(OR($B54="",$J54=""),"",IFERROR(INDEX(CHOOSE($J54,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B54,CHOOSE($J54,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J54,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <f>IF(OR($B54="",$J54=""),"",IFERROR(INDEX(CHOOSE($J54,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B54,CHOOSE($J54,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J54,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G54" t="str">
+        <f>IF(OR($B54="",$J54=""),"",IFERROR(INDEX(CHOOSE($J54,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B54,CHOOSE($J54,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J54,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H54" s="6"/>
+      <c r="I54" s="6"/>
+      <c r="J54" t="str">
+        <f>IFERROR(MATCH($C54,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D55" t="str">
+        <f>IF(OR($B55="",$J55=""),"",IFERROR(INDEX(CHOOSE($J55,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B55,CHOOSE($J55,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J55,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <f>IF(OR($B55="",$J55=""),"",IFERROR(INDEX(CHOOSE($J55,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B55,CHOOSE($J55,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J55,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <f>IF(OR($B55="",$J55=""),"",IFERROR(INDEX(CHOOSE($J55,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B55,CHOOSE($J55,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J55,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G55" t="str">
+        <f>IF(OR($B55="",$J55=""),"",IFERROR(INDEX(CHOOSE($J55,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B55,CHOOSE($J55,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J55,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H55" s="6"/>
+      <c r="I55" s="6"/>
+      <c r="J55" t="str">
+        <f>IFERROR(MATCH($C55,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D56" t="str">
+        <f>IF(OR($B56="",$J56=""),"",IFERROR(INDEX(CHOOSE($J56,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B56,CHOOSE($J56,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J56,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <f>IF(OR($B56="",$J56=""),"",IFERROR(INDEX(CHOOSE($J56,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B56,CHOOSE($J56,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J56,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <f>IF(OR($B56="",$J56=""),"",IFERROR(INDEX(CHOOSE($J56,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B56,CHOOSE($J56,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J56,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G56" t="str">
+        <f>IF(OR($B56="",$J56=""),"",IFERROR(INDEX(CHOOSE($J56,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B56,CHOOSE($J56,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J56,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H56" s="6"/>
+      <c r="I56" s="6"/>
+      <c r="J56" t="str">
+        <f>IFERROR(MATCH($C56,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D57" t="str">
+        <f>IF(OR($B57="",$J57=""),"",IFERROR(INDEX(CHOOSE($J57,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B57,CHOOSE($J57,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J57,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E57" t="str">
+        <f>IF(OR($B57="",$J57=""),"",IFERROR(INDEX(CHOOSE($J57,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B57,CHOOSE($J57,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J57,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <f>IF(OR($B57="",$J57=""),"",IFERROR(INDEX(CHOOSE($J57,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B57,CHOOSE($J57,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J57,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G57" t="str">
+        <f>IF(OR($B57="",$J57=""),"",IFERROR(INDEX(CHOOSE($J57,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B57,CHOOSE($J57,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J57,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H57" s="6"/>
+      <c r="I57" s="6"/>
+      <c r="J57" t="str">
+        <f>IFERROR(MATCH($C57,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D58" t="str">
+        <f>IF(OR($B58="",$J58=""),"",IFERROR(INDEX(CHOOSE($J58,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B58,CHOOSE($J58,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J58,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E58" t="str">
+        <f>IF(OR($B58="",$J58=""),"",IFERROR(INDEX(CHOOSE($J58,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B58,CHOOSE($J58,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J58,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <f>IF(OR($B58="",$J58=""),"",IFERROR(INDEX(CHOOSE($J58,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B58,CHOOSE($J58,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J58,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G58" t="str">
+        <f>IF(OR($B58="",$J58=""),"",IFERROR(INDEX(CHOOSE($J58,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B58,CHOOSE($J58,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J58,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H58" s="6"/>
+      <c r="I58" s="6"/>
+      <c r="J58" t="str">
+        <f>IFERROR(MATCH($C58,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D59" t="str">
+        <f>IF(OR($B59="",$J59=""),"",IFERROR(INDEX(CHOOSE($J59,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B59,CHOOSE($J59,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J59,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E59" t="str">
+        <f>IF(OR($B59="",$J59=""),"",IFERROR(INDEX(CHOOSE($J59,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B59,CHOOSE($J59,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J59,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F59" t="str">
+        <f>IF(OR($B59="",$J59=""),"",IFERROR(INDEX(CHOOSE($J59,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B59,CHOOSE($J59,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J59,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <f>IF(OR($B59="",$J59=""),"",IFERROR(INDEX(CHOOSE($J59,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B59,CHOOSE($J59,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J59,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H59" s="6"/>
+      <c r="I59" s="6"/>
+      <c r="J59" t="str">
+        <f>IFERROR(MATCH($C59,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D60" t="str">
+        <f>IF(OR($B60="",$J60=""),"",IFERROR(INDEX(CHOOSE($J60,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B60,CHOOSE($J60,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J60,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E60" t="str">
+        <f>IF(OR($B60="",$J60=""),"",IFERROR(INDEX(CHOOSE($J60,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B60,CHOOSE($J60,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J60,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <f>IF(OR($B60="",$J60=""),"",IFERROR(INDEX(CHOOSE($J60,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B60,CHOOSE($J60,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J60,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G60" t="str">
+        <f>IF(OR($B60="",$J60=""),"",IFERROR(INDEX(CHOOSE($J60,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B60,CHOOSE($J60,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J60,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" t="str">
+        <f>IFERROR(MATCH($C60,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D61" t="str">
+        <f>IF(OR($B61="",$J61=""),"",IFERROR(INDEX(CHOOSE($J61,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B61,CHOOSE($J61,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J61,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E61" t="str">
+        <f>IF(OR($B61="",$J61=""),"",IFERROR(INDEX(CHOOSE($J61,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B61,CHOOSE($J61,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J61,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <f>IF(OR($B61="",$J61=""),"",IFERROR(INDEX(CHOOSE($J61,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B61,CHOOSE($J61,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J61,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G61" t="str">
+        <f>IF(OR($B61="",$J61=""),"",IFERROR(INDEX(CHOOSE($J61,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B61,CHOOSE($J61,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J61,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" t="str">
+        <f>IFERROR(MATCH($C61,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D62" t="str">
+        <f>IF(OR($B62="",$J62=""),"",IFERROR(INDEX(CHOOSE($J62,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B62,CHOOSE($J62,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J62,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E62" t="str">
+        <f>IF(OR($B62="",$J62=""),"",IFERROR(INDEX(CHOOSE($J62,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B62,CHOOSE($J62,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J62,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <f>IF(OR($B62="",$J62=""),"",IFERROR(INDEX(CHOOSE($J62,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B62,CHOOSE($J62,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J62,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G62" t="str">
+        <f>IF(OR($B62="",$J62=""),"",IFERROR(INDEX(CHOOSE($J62,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B62,CHOOSE($J62,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J62,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H62" s="6"/>
+      <c r="I62" s="6"/>
+      <c r="J62" t="str">
+        <f>IFERROR(MATCH($C62,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D63" t="str">
+        <f>IF(OR($B63="",$J63=""),"",IFERROR(INDEX(CHOOSE($J63,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B63,CHOOSE($J63,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J63,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E63" t="str">
+        <f>IF(OR($B63="",$J63=""),"",IFERROR(INDEX(CHOOSE($J63,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B63,CHOOSE($J63,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J63,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <f>IF(OR($B63="",$J63=""),"",IFERROR(INDEX(CHOOSE($J63,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B63,CHOOSE($J63,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J63,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G63" t="str">
+        <f>IF(OR($B63="",$J63=""),"",IFERROR(INDEX(CHOOSE($J63,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B63,CHOOSE($J63,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J63,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H63" s="6"/>
+      <c r="I63" s="6"/>
+      <c r="J63" t="str">
+        <f>IFERROR(MATCH($C63,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D64" t="str">
+        <f>IF(OR($B64="",$J64=""),"",IFERROR(INDEX(CHOOSE($J64,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B64,CHOOSE($J64,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J64,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E64" t="str">
+        <f>IF(OR($B64="",$J64=""),"",IFERROR(INDEX(CHOOSE($J64,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B64,CHOOSE($J64,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J64,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <f>IF(OR($B64="",$J64=""),"",IFERROR(INDEX(CHOOSE($J64,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B64,CHOOSE($J64,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J64,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G64" t="str">
+        <f>IF(OR($B64="",$J64=""),"",IFERROR(INDEX(CHOOSE($J64,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B64,CHOOSE($J64,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J64,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H64" s="6"/>
+      <c r="I64" s="6"/>
+      <c r="J64" t="str">
+        <f>IFERROR(MATCH($C64,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D65" t="str">
+        <f>IF(OR($B65="",$J65=""),"",IFERROR(INDEX(CHOOSE($J65,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B65,CHOOSE($J65,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J65,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E65" t="str">
+        <f>IF(OR($B65="",$J65=""),"",IFERROR(INDEX(CHOOSE($J65,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B65,CHOOSE($J65,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J65,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <f>IF(OR($B65="",$J65=""),"",IFERROR(INDEX(CHOOSE($J65,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B65,CHOOSE($J65,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J65,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G65" t="str">
+        <f>IF(OR($B65="",$J65=""),"",IFERROR(INDEX(CHOOSE($J65,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B65,CHOOSE($J65,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J65,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H65" s="6"/>
+      <c r="I65" s="6"/>
+      <c r="J65" t="str">
+        <f>IFERROR(MATCH($C65,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D66" t="str">
+        <f>IF(OR($B66="",$J66=""),"",IFERROR(INDEX(CHOOSE($J66,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B66,CHOOSE($J66,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J66,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E66" t="str">
+        <f>IF(OR($B66="",$J66=""),"",IFERROR(INDEX(CHOOSE($J66,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B66,CHOOSE($J66,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J66,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <f>IF(OR($B66="",$J66=""),"",IFERROR(INDEX(CHOOSE($J66,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B66,CHOOSE($J66,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J66,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G66" t="str">
+        <f>IF(OR($B66="",$J66=""),"",IFERROR(INDEX(CHOOSE($J66,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B66,CHOOSE($J66,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J66,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" t="str">
+        <f>IFERROR(MATCH($C66,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D67" t="str">
+        <f>IF(OR($B67="",$J67=""),"",IFERROR(INDEX(CHOOSE($J67,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B67,CHOOSE($J67,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J67,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E67" t="str">
+        <f>IF(OR($B67="",$J67=""),"",IFERROR(INDEX(CHOOSE($J67,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B67,CHOOSE($J67,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J67,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <f>IF(OR($B67="",$J67=""),"",IFERROR(INDEX(CHOOSE($J67,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B67,CHOOSE($J67,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J67,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G67" t="str">
+        <f>IF(OR($B67="",$J67=""),"",IFERROR(INDEX(CHOOSE($J67,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B67,CHOOSE($J67,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J67,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" t="str">
+        <f>IFERROR(MATCH($C67,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D68" t="str">
+        <f>IF(OR($B68="",$J68=""),"",IFERROR(INDEX(CHOOSE($J68,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B68,CHOOSE($J68,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J68,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E68" t="str">
+        <f>IF(OR($B68="",$J68=""),"",IFERROR(INDEX(CHOOSE($J68,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B68,CHOOSE($J68,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J68,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <f>IF(OR($B68="",$J68=""),"",IFERROR(INDEX(CHOOSE($J68,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B68,CHOOSE($J68,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J68,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <f>IF(OR($B68="",$J68=""),"",IFERROR(INDEX(CHOOSE($J68,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B68,CHOOSE($J68,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J68,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" t="str">
+        <f>IFERROR(MATCH($C68,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D69" t="str">
+        <f>IF(OR($B69="",$J69=""),"",IFERROR(INDEX(CHOOSE($J69,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B69,CHOOSE($J69,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J69,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E69" t="str">
+        <f>IF(OR($B69="",$J69=""),"",IFERROR(INDEX(CHOOSE($J69,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B69,CHOOSE($J69,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J69,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <f>IF(OR($B69="",$J69=""),"",IFERROR(INDEX(CHOOSE($J69,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B69,CHOOSE($J69,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J69,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <f>IF(OR($B69="",$J69=""),"",IFERROR(INDEX(CHOOSE($J69,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B69,CHOOSE($J69,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J69,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" t="str">
+        <f>IFERROR(MATCH($C69,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D70" t="str">
+        <f>IF(OR($B70="",$J70=""),"",IFERROR(INDEX(CHOOSE($J70,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B70,CHOOSE($J70,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J70,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E70" t="str">
+        <f>IF(OR($B70="",$J70=""),"",IFERROR(INDEX(CHOOSE($J70,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B70,CHOOSE($J70,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J70,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <f>IF(OR($B70="",$J70=""),"",IFERROR(INDEX(CHOOSE($J70,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B70,CHOOSE($J70,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J70,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G70" t="str">
+        <f>IF(OR($B70="",$J70=""),"",IFERROR(INDEX(CHOOSE($J70,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B70,CHOOSE($J70,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J70,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" t="str">
+        <f>IFERROR(MATCH($C70,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D71" t="str">
+        <f>IF(OR($B71="",$J71=""),"",IFERROR(INDEX(CHOOSE($J71,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B71,CHOOSE($J71,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J71,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E71" t="str">
+        <f>IF(OR($B71="",$J71=""),"",IFERROR(INDEX(CHOOSE($J71,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B71,CHOOSE($J71,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J71,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <f>IF(OR($B71="",$J71=""),"",IFERROR(INDEX(CHOOSE($J71,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B71,CHOOSE($J71,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J71,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G71" t="str">
+        <f>IF(OR($B71="",$J71=""),"",IFERROR(INDEX(CHOOSE($J71,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B71,CHOOSE($J71,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J71,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" t="str">
+        <f>IFERROR(MATCH($C71,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D72" t="str">
+        <f>IF(OR($B72="",$J72=""),"",IFERROR(INDEX(CHOOSE($J72,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B72,CHOOSE($J72,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J72,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E72" t="str">
+        <f>IF(OR($B72="",$J72=""),"",IFERROR(INDEX(CHOOSE($J72,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B72,CHOOSE($J72,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J72,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F72" t="str">
+        <f>IF(OR($B72="",$J72=""),"",IFERROR(INDEX(CHOOSE($J72,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B72,CHOOSE($J72,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J72,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <f>IF(OR($B72="",$J72=""),"",IFERROR(INDEX(CHOOSE($J72,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B72,CHOOSE($J72,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J72,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" t="str">
+        <f>IFERROR(MATCH($C72,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D73" t="str">
+        <f>IF(OR($B73="",$J73=""),"",IFERROR(INDEX(CHOOSE($J73,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B73,CHOOSE($J73,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J73,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <f>IF(OR($B73="",$J73=""),"",IFERROR(INDEX(CHOOSE($J73,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B73,CHOOSE($J73,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J73,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <f>IF(OR($B73="",$J73=""),"",IFERROR(INDEX(CHOOSE($J73,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B73,CHOOSE($J73,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J73,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G73" t="str">
+        <f>IF(OR($B73="",$J73=""),"",IFERROR(INDEX(CHOOSE($J73,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B73,CHOOSE($J73,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J73,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" t="str">
+        <f>IFERROR(MATCH($C73,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D74" t="str">
+        <f>IF(OR($B74="",$J74=""),"",IFERROR(INDEX(CHOOSE($J74,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B74,CHOOSE($J74,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J74,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <f>IF(OR($B74="",$J74=""),"",IFERROR(INDEX(CHOOSE($J74,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B74,CHOOSE($J74,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J74,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F74" t="str">
+        <f>IF(OR($B74="",$J74=""),"",IFERROR(INDEX(CHOOSE($J74,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B74,CHOOSE($J74,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J74,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <f>IF(OR($B74="",$J74=""),"",IFERROR(INDEX(CHOOSE($J74,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B74,CHOOSE($J74,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J74,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H74" s="6"/>
+      <c r="I74" s="6"/>
+      <c r="J74" t="str">
+        <f>IFERROR(MATCH($C74,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D75" t="str">
+        <f>IF(OR($B75="",$J75=""),"",IFERROR(INDEX(CHOOSE($J75,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B75,CHOOSE($J75,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J75,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E75" t="str">
+        <f>IF(OR($B75="",$J75=""),"",IFERROR(INDEX(CHOOSE($J75,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B75,CHOOSE($J75,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J75,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F75" t="str">
+        <f>IF(OR($B75="",$J75=""),"",IFERROR(INDEX(CHOOSE($J75,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B75,CHOOSE($J75,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J75,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G75" t="str">
+        <f>IF(OR($B75="",$J75=""),"",IFERROR(INDEX(CHOOSE($J75,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B75,CHOOSE($J75,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J75,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H75" s="6"/>
+      <c r="I75" s="6"/>
+      <c r="J75" t="str">
+        <f>IFERROR(MATCH($C75,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D76" t="str">
+        <f>IF(OR($B76="",$J76=""),"",IFERROR(INDEX(CHOOSE($J76,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B76,CHOOSE($J76,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J76,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E76" t="str">
+        <f>IF(OR($B76="",$J76=""),"",IFERROR(INDEX(CHOOSE($J76,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B76,CHOOSE($J76,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J76,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <f>IF(OR($B76="",$J76=""),"",IFERROR(INDEX(CHOOSE($J76,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B76,CHOOSE($J76,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J76,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G76" t="str">
+        <f>IF(OR($B76="",$J76=""),"",IFERROR(INDEX(CHOOSE($J76,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B76,CHOOSE($J76,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J76,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" t="str">
+        <f>IFERROR(MATCH($C76,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D77" t="str">
+        <f>IF(OR($B77="",$J77=""),"",IFERROR(INDEX(CHOOSE($J77,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B77,CHOOSE($J77,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J77,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E77" t="str">
+        <f>IF(OR($B77="",$J77=""),"",IFERROR(INDEX(CHOOSE($J77,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B77,CHOOSE($J77,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J77,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F77" t="str">
+        <f>IF(OR($B77="",$J77=""),"",IFERROR(INDEX(CHOOSE($J77,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B77,CHOOSE($J77,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J77,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <f>IF(OR($B77="",$J77=""),"",IFERROR(INDEX(CHOOSE($J77,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B77,CHOOSE($J77,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J77,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H77" s="6"/>
+      <c r="I77" s="6"/>
+      <c r="J77" t="str">
+        <f>IFERROR(MATCH($C77,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D78" t="str">
+        <f>IF(OR($B78="",$J78=""),"",IFERROR(INDEX(CHOOSE($J78,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B78,CHOOSE($J78,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J78,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E78" t="str">
+        <f>IF(OR($B78="",$J78=""),"",IFERROR(INDEX(CHOOSE($J78,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B78,CHOOSE($J78,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J78,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <f>IF(OR($B78="",$J78=""),"",IFERROR(INDEX(CHOOSE($J78,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B78,CHOOSE($J78,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J78,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G78" t="str">
+        <f>IF(OR($B78="",$J78=""),"",IFERROR(INDEX(CHOOSE($J78,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B78,CHOOSE($J78,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J78,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H78" s="6"/>
+      <c r="I78" s="6"/>
+      <c r="J78" t="str">
+        <f>IFERROR(MATCH($C78,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D79" t="str">
+        <f>IF(OR($B79="",$J79=""),"",IFERROR(INDEX(CHOOSE($J79,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B79,CHOOSE($J79,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J79,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E79" t="str">
+        <f>IF(OR($B79="",$J79=""),"",IFERROR(INDEX(CHOOSE($J79,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B79,CHOOSE($J79,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J79,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <f>IF(OR($B79="",$J79=""),"",IFERROR(INDEX(CHOOSE($J79,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B79,CHOOSE($J79,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J79,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G79" t="str">
+        <f>IF(OR($B79="",$J79=""),"",IFERROR(INDEX(CHOOSE($J79,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B79,CHOOSE($J79,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J79,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H79" s="6"/>
+      <c r="I79" s="6"/>
+      <c r="J79" t="str">
+        <f>IFERROR(MATCH($C79,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D80" t="str">
+        <f>IF(OR($B80="",$J80=""),"",IFERROR(INDEX(CHOOSE($J80,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B80,CHOOSE($J80,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J80,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E80" t="str">
+        <f>IF(OR($B80="",$J80=""),"",IFERROR(INDEX(CHOOSE($J80,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B80,CHOOSE($J80,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J80,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F80" t="str">
+        <f>IF(OR($B80="",$J80=""),"",IFERROR(INDEX(CHOOSE($J80,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B80,CHOOSE($J80,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J80,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G80" t="str">
+        <f>IF(OR($B80="",$J80=""),"",IFERROR(INDEX(CHOOSE($J80,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B80,CHOOSE($J80,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J80,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" t="str">
+        <f>IFERROR(MATCH($C80,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D81" t="str">
+        <f>IF(OR($B81="",$J81=""),"",IFERROR(INDEX(CHOOSE($J81,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B81,CHOOSE($J81,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J81,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E81" t="str">
+        <f>IF(OR($B81="",$J81=""),"",IFERROR(INDEX(CHOOSE($J81,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B81,CHOOSE($J81,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J81,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <f>IF(OR($B81="",$J81=""),"",IFERROR(INDEX(CHOOSE($J81,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B81,CHOOSE($J81,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J81,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G81" t="str">
+        <f>IF(OR($B81="",$J81=""),"",IFERROR(INDEX(CHOOSE($J81,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B81,CHOOSE($J81,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J81,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H81" s="6"/>
+      <c r="I81" s="6"/>
+      <c r="J81" t="str">
+        <f>IFERROR(MATCH($C81,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D82" t="str">
+        <f>IF(OR($B82="",$J82=""),"",IFERROR(INDEX(CHOOSE($J82,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B82,CHOOSE($J82,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J82,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E82" t="str">
+        <f>IF(OR($B82="",$J82=""),"",IFERROR(INDEX(CHOOSE($J82,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B82,CHOOSE($J82,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J82,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <f>IF(OR($B82="",$J82=""),"",IFERROR(INDEX(CHOOSE($J82,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B82,CHOOSE($J82,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J82,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G82" t="str">
+        <f>IF(OR($B82="",$J82=""),"",IFERROR(INDEX(CHOOSE($J82,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B82,CHOOSE($J82,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J82,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H82" s="6"/>
+      <c r="I82" s="6"/>
+      <c r="J82" t="str">
+        <f>IFERROR(MATCH($C82,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D83" t="str">
+        <f>IF(OR($B83="",$J83=""),"",IFERROR(INDEX(CHOOSE($J83,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B83,CHOOSE($J83,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J83,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E83" t="str">
+        <f>IF(OR($B83="",$J83=""),"",IFERROR(INDEX(CHOOSE($J83,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B83,CHOOSE($J83,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J83,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <f>IF(OR($B83="",$J83=""),"",IFERROR(INDEX(CHOOSE($J83,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B83,CHOOSE($J83,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J83,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G83" t="str">
+        <f>IF(OR($B83="",$J83=""),"",IFERROR(INDEX(CHOOSE($J83,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B83,CHOOSE($J83,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J83,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H83" s="6"/>
+      <c r="I83" s="6"/>
+      <c r="J83" t="str">
+        <f>IFERROR(MATCH($C83,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D84" t="str">
+        <f>IF(OR($B84="",$J84=""),"",IFERROR(INDEX(CHOOSE($J84,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B84,CHOOSE($J84,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J84,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E84" t="str">
+        <f>IF(OR($B84="",$J84=""),"",IFERROR(INDEX(CHOOSE($J84,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B84,CHOOSE($J84,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J84,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <f>IF(OR($B84="",$J84=""),"",IFERROR(INDEX(CHOOSE($J84,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B84,CHOOSE($J84,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J84,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G84" t="str">
+        <f>IF(OR($B84="",$J84=""),"",IFERROR(INDEX(CHOOSE($J84,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B84,CHOOSE($J84,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J84,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H84" s="6"/>
+      <c r="I84" s="6"/>
+      <c r="J84" t="str">
+        <f>IFERROR(MATCH($C84,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D85" t="str">
+        <f>IF(OR($B85="",$J85=""),"",IFERROR(INDEX(CHOOSE($J85,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B85,CHOOSE($J85,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J85,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E85" t="str">
+        <f>IF(OR($B85="",$J85=""),"",IFERROR(INDEX(CHOOSE($J85,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B85,CHOOSE($J85,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J85,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <f>IF(OR($B85="",$J85=""),"",IFERROR(INDEX(CHOOSE($J85,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B85,CHOOSE($J85,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J85,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <f>IF(OR($B85="",$J85=""),"",IFERROR(INDEX(CHOOSE($J85,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B85,CHOOSE($J85,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J85,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H85" s="6"/>
+      <c r="I85" s="6"/>
+      <c r="J85" t="str">
+        <f>IFERROR(MATCH($C85,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D86" t="str">
+        <f>IF(OR($B86="",$J86=""),"",IFERROR(INDEX(CHOOSE($J86,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B86,CHOOSE($J86,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J86,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E86" t="str">
+        <f>IF(OR($B86="",$J86=""),"",IFERROR(INDEX(CHOOSE($J86,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B86,CHOOSE($J86,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J86,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <f>IF(OR($B86="",$J86=""),"",IFERROR(INDEX(CHOOSE($J86,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B86,CHOOSE($J86,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J86,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <f>IF(OR($B86="",$J86=""),"",IFERROR(INDEX(CHOOSE($J86,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B86,CHOOSE($J86,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J86,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H86" s="6"/>
+      <c r="I86" s="6"/>
+      <c r="J86" t="str">
+        <f>IFERROR(MATCH($C86,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D87" t="str">
+        <f>IF(OR($B87="",$J87=""),"",IFERROR(INDEX(CHOOSE($J87,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B87,CHOOSE($J87,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J87,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E87" t="str">
+        <f>IF(OR($B87="",$J87=""),"",IFERROR(INDEX(CHOOSE($J87,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B87,CHOOSE($J87,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J87,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <f>IF(OR($B87="",$J87=""),"",IFERROR(INDEX(CHOOSE($J87,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B87,CHOOSE($J87,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J87,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <f>IF(OR($B87="",$J87=""),"",IFERROR(INDEX(CHOOSE($J87,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B87,CHOOSE($J87,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J87,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H87" s="6"/>
+      <c r="I87" s="6"/>
+      <c r="J87" t="str">
+        <f>IFERROR(MATCH($C87,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D88" t="str">
+        <f>IF(OR($B88="",$J88=""),"",IFERROR(INDEX(CHOOSE($J88,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B88,CHOOSE($J88,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J88,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E88" t="str">
+        <f>IF(OR($B88="",$J88=""),"",IFERROR(INDEX(CHOOSE($J88,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B88,CHOOSE($J88,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J88,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <f>IF(OR($B88="",$J88=""),"",IFERROR(INDEX(CHOOSE($J88,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B88,CHOOSE($J88,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J88,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <f>IF(OR($B88="",$J88=""),"",IFERROR(INDEX(CHOOSE($J88,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B88,CHOOSE($J88,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J88,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" t="str">
+        <f>IFERROR(MATCH($C88,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D89" t="str">
+        <f>IF(OR($B89="",$J89=""),"",IFERROR(INDEX(CHOOSE($J89,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B89,CHOOSE($J89,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J89,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E89" t="str">
+        <f>IF(OR($B89="",$J89=""),"",IFERROR(INDEX(CHOOSE($J89,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B89,CHOOSE($J89,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J89,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <f>IF(OR($B89="",$J89=""),"",IFERROR(INDEX(CHOOSE($J89,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B89,CHOOSE($J89,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J89,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <f>IF(OR($B89="",$J89=""),"",IFERROR(INDEX(CHOOSE($J89,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B89,CHOOSE($J89,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J89,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H89" s="6"/>
+      <c r="I89" s="6"/>
+      <c r="J89" t="str">
+        <f>IFERROR(MATCH($C89,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D90" t="str">
+        <f>IF(OR($B90="",$J90=""),"",IFERROR(INDEX(CHOOSE($J90,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B90,CHOOSE($J90,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J90,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E90" t="str">
+        <f>IF(OR($B90="",$J90=""),"",IFERROR(INDEX(CHOOSE($J90,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B90,CHOOSE($J90,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J90,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <f>IF(OR($B90="",$J90=""),"",IFERROR(INDEX(CHOOSE($J90,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B90,CHOOSE($J90,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J90,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <f>IF(OR($B90="",$J90=""),"",IFERROR(INDEX(CHOOSE($J90,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B90,CHOOSE($J90,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J90,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H90" s="6"/>
+      <c r="I90" s="6"/>
+      <c r="J90" t="str">
+        <f>IFERROR(MATCH($C90,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D91" t="str">
+        <f>IF(OR($B91="",$J91=""),"",IFERROR(INDEX(CHOOSE($J91,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B91,CHOOSE($J91,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J91,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E91" t="str">
+        <f>IF(OR($B91="",$J91=""),"",IFERROR(INDEX(CHOOSE($J91,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B91,CHOOSE($J91,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J91,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <f>IF(OR($B91="",$J91=""),"",IFERROR(INDEX(CHOOSE($J91,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B91,CHOOSE($J91,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J91,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <f>IF(OR($B91="",$J91=""),"",IFERROR(INDEX(CHOOSE($J91,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B91,CHOOSE($J91,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J91,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H91" s="6"/>
+      <c r="I91" s="6"/>
+      <c r="J91" t="str">
+        <f>IFERROR(MATCH($C91,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D92" t="str">
+        <f>IF(OR($B92="",$J92=""),"",IFERROR(INDEX(CHOOSE($J92,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B92,CHOOSE($J92,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J92,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E92" t="str">
+        <f>IF(OR($B92="",$J92=""),"",IFERROR(INDEX(CHOOSE($J92,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B92,CHOOSE($J92,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J92,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F92" t="str">
+        <f>IF(OR($B92="",$J92=""),"",IFERROR(INDEX(CHOOSE($J92,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B92,CHOOSE($J92,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J92,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G92" t="str">
+        <f>IF(OR($B92="",$J92=""),"",IFERROR(INDEX(CHOOSE($J92,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B92,CHOOSE($J92,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J92,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H92" s="6"/>
+      <c r="I92" s="6"/>
+      <c r="J92" t="str">
+        <f>IFERROR(MATCH($C92,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D93" t="str">
+        <f>IF(OR($B93="",$J93=""),"",IFERROR(INDEX(CHOOSE($J93,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B93,CHOOSE($J93,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J93,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E93" t="str">
+        <f>IF(OR($B93="",$J93=""),"",IFERROR(INDEX(CHOOSE($J93,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B93,CHOOSE($J93,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J93,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <f>IF(OR($B93="",$J93=""),"",IFERROR(INDEX(CHOOSE($J93,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B93,CHOOSE($J93,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J93,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G93" t="str">
+        <f>IF(OR($B93="",$J93=""),"",IFERROR(INDEX(CHOOSE($J93,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B93,CHOOSE($J93,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J93,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H93" s="6"/>
+      <c r="I93" s="6"/>
+      <c r="J93" t="str">
+        <f>IFERROR(MATCH($C93,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D94" t="str">
+        <f>IF(OR($B94="",$J94=""),"",IFERROR(INDEX(CHOOSE($J94,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B94,CHOOSE($J94,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J94,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E94" t="str">
+        <f>IF(OR($B94="",$J94=""),"",IFERROR(INDEX(CHOOSE($J94,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B94,CHOOSE($J94,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J94,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <f>IF(OR($B94="",$J94=""),"",IFERROR(INDEX(CHOOSE($J94,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B94,CHOOSE($J94,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J94,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G94" t="str">
+        <f>IF(OR($B94="",$J94=""),"",IFERROR(INDEX(CHOOSE($J94,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B94,CHOOSE($J94,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J94,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H94" s="6"/>
+      <c r="I94" s="6"/>
+      <c r="J94" t="str">
+        <f>IFERROR(MATCH($C94,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D95" t="str">
+        <f>IF(OR($B95="",$J95=""),"",IFERROR(INDEX(CHOOSE($J95,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B95,CHOOSE($J95,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J95,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E95" t="str">
+        <f>IF(OR($B95="",$J95=""),"",IFERROR(INDEX(CHOOSE($J95,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B95,CHOOSE($J95,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J95,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F95" t="str">
+        <f>IF(OR($B95="",$J95=""),"",IFERROR(INDEX(CHOOSE($J95,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B95,CHOOSE($J95,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J95,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <f>IF(OR($B95="",$J95=""),"",IFERROR(INDEX(CHOOSE($J95,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B95,CHOOSE($J95,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J95,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H95" s="6"/>
+      <c r="I95" s="6"/>
+      <c r="J95" t="str">
+        <f>IFERROR(MATCH($C95,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D96" t="str">
+        <f>IF(OR($B96="",$J96=""),"",IFERROR(INDEX(CHOOSE($J96,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B96,CHOOSE($J96,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J96,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E96" t="str">
+        <f>IF(OR($B96="",$J96=""),"",IFERROR(INDEX(CHOOSE($J96,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B96,CHOOSE($J96,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J96,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <f>IF(OR($B96="",$J96=""),"",IFERROR(INDEX(CHOOSE($J96,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B96,CHOOSE($J96,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J96,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G96" t="str">
+        <f>IF(OR($B96="",$J96=""),"",IFERROR(INDEX(CHOOSE($J96,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B96,CHOOSE($J96,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J96,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" t="str">
+        <f>IFERROR(MATCH($C96,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D97" t="str">
+        <f>IF(OR($B97="",$J97=""),"",IFERROR(INDEX(CHOOSE($J97,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B97,CHOOSE($J97,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J97,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E97" t="str">
+        <f>IF(OR($B97="",$J97=""),"",IFERROR(INDEX(CHOOSE($J97,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B97,CHOOSE($J97,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J97,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <f>IF(OR($B97="",$J97=""),"",IFERROR(INDEX(CHOOSE($J97,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B97,CHOOSE($J97,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J97,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G97" t="str">
+        <f>IF(OR($B97="",$J97=""),"",IFERROR(INDEX(CHOOSE($J97,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B97,CHOOSE($J97,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J97,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H97" s="6"/>
+      <c r="I97" s="6"/>
+      <c r="J97" t="str">
+        <f>IFERROR(MATCH($C97,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D98" t="str">
+        <f>IF(OR($B98="",$J98=""),"",IFERROR(INDEX(CHOOSE($J98,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B98,CHOOSE($J98,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J98,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <f>IF(OR($B98="",$J98=""),"",IFERROR(INDEX(CHOOSE($J98,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B98,CHOOSE($J98,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J98,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <f>IF(OR($B98="",$J98=""),"",IFERROR(INDEX(CHOOSE($J98,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B98,CHOOSE($J98,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J98,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G98" t="str">
+        <f>IF(OR($B98="",$J98=""),"",IFERROR(INDEX(CHOOSE($J98,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B98,CHOOSE($J98,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J98,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H98" s="6"/>
+      <c r="I98" s="6"/>
+      <c r="J98" t="str">
+        <f>IFERROR(MATCH($C98,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D99" t="str">
+        <f>IF(OR($B99="",$J99=""),"",IFERROR(INDEX(CHOOSE($J99,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B99,CHOOSE($J99,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J99,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <f>IF(OR($B99="",$J99=""),"",IFERROR(INDEX(CHOOSE($J99,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B99,CHOOSE($J99,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J99,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <f>IF(OR($B99="",$J99=""),"",IFERROR(INDEX(CHOOSE($J99,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B99,CHOOSE($J99,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J99,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G99" t="str">
+        <f>IF(OR($B99="",$J99=""),"",IFERROR(INDEX(CHOOSE($J99,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B99,CHOOSE($J99,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J99,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H99" s="6"/>
+      <c r="I99" s="6"/>
+      <c r="J99" t="str">
+        <f>IFERROR(MATCH($C99,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D100" t="str">
+        <f>IF(OR($B100="",$J100=""),"",IFERROR(INDEX(CHOOSE($J100,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B100,CHOOSE($J100,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J100,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <f>IF(OR($B100="",$J100=""),"",IFERROR(INDEX(CHOOSE($J100,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B100,CHOOSE($J100,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J100,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <f>IF(OR($B100="",$J100=""),"",IFERROR(INDEX(CHOOSE($J100,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B100,CHOOSE($J100,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J100,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G100" t="str">
+        <f>IF(OR($B100="",$J100=""),"",IFERROR(INDEX(CHOOSE($J100,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B100,CHOOSE($J100,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J100,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H100" s="6"/>
+      <c r="I100" s="6"/>
+      <c r="J100" t="str">
+        <f>IFERROR(MATCH($C100,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="D101" t="str">
+        <f>IF(OR($B101="",$J101=""),"",IFERROR(INDEX(CHOOSE($J101,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B101,CHOOSE($J101,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(D$1,CHOOSE($J101,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <f>IF(OR($B101="",$J101=""),"",IFERROR(INDEX(CHOOSE($J101,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B101,CHOOSE($J101,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(E$1,CHOOSE($J101,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="F101" t="str">
+        <f>IF(OR($B101="",$J101=""),"",IFERROR(INDEX(CHOOSE($J101,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B101,CHOOSE($J101,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(F$1,CHOOSE($J101,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="G101" t="str">
+        <f>IF(OR($B101="",$J101=""),"",IFERROR(INDEX(CHOOSE($J101,prod_her!$A:$J,prod_ins!$A:$J,prod_fun!$A:$J,prod_fer!$A:$L),MATCH($B101,CHOOSE($J101,prod_her!$A:$A,prod_ins!$A:$A,prod_fun!$A:$A,prod_fer!$A:$A),0),MATCH(G$1,CHOOSE($J101,prod_her!$1:$1,prod_ins!$1:$1,prod_fun!$1:$1,prod_fer!$1:$1),0)),""))</f>
+        <v/>
+      </c>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6"/>
+      <c r="J101" t="str">
+        <f>IFERROR(MATCH($C101,{"herbicide";"insecticide";"fungicide";"fertilizer"},0),"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AC11EAC1-9BA5-EA4D-B068-44980A8605C8}">
+          <x14:formula1>
+            <xm:f>ref!$A$22:$A$24</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C31</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD323E38-B5EE-7946-941F-1D3A439D6394}">
   <dimension ref="A1:O479"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -5427,10 +9274,10 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>810</v>
+        <v>802</v>
       </c>
       <c r="C16" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="K16" t="s">
         <v>167</v>
@@ -5444,10 +9291,10 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="C17" t="s">
-        <v>855</v>
+        <v>845</v>
       </c>
       <c r="K17" t="s">
         <v>168</v>
@@ -5461,10 +9308,10 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="C18" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="K18" t="s">
         <v>169</v>
@@ -5478,10 +9325,10 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="C19" t="s">
-        <v>856</v>
+        <v>846</v>
       </c>
       <c r="L19" s="1"/>
       <c r="O19" t="s">
@@ -5499,16 +9346,25 @@
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>1051</v>
+      </c>
       <c r="O22" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>1052</v>
+      </c>
       <c r="O23" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>1053</v>
+      </c>
       <c r="O24" t="s">
         <v>311</v>
       </c>
@@ -8936,7 +12792,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -10460,10 +14316,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="C1" t="s">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>3</v>
@@ -10483,7 +14339,7 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>800</v>
+        <v>792</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>284</v>
@@ -10503,10 +14359,10 @@
         <v>38</v>
       </c>
       <c r="C3" t="s">
-        <v>801</v>
+        <v>793</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>803</v>
+        <v>795</v>
       </c>
       <c r="E3">
         <v>40</v>
@@ -10523,10 +14379,10 @@
         <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>802</v>
+        <v>794</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>804</v>
+        <v>796</v>
       </c>
       <c r="E4">
         <v>60</v>
@@ -10570,16 +14426,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DD592B2-2C41-1244-8687-204538C3610A}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="B1" t="s">
         <v>761</v>
@@ -10600,24 +14456,18 @@
         <v>192</v>
       </c>
       <c r="H1" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="I1" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="J1" t="s">
-        <v>848</v>
-      </c>
-      <c r="K1" t="s">
-        <v>847</v>
-      </c>
-      <c r="L1" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="B2" t="s">
         <v>763</v>
@@ -10628,38 +14478,31 @@
       <c r="D2" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" t="s">
+        <v>831</v>
+      </c>
+      <c r="I2">
+        <v>500</v>
+      </c>
+      <c r="J2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>800</v>
+      </c>
+      <c r="B3" t="s">
         <v>767</v>
-      </c>
-      <c r="H2" t="s">
-        <v>839</v>
-      </c>
-      <c r="I2">
-        <v>380</v>
-      </c>
-      <c r="J2">
-        <v>0.5</v>
-      </c>
-      <c r="K2">
-        <v>0.05</v>
-      </c>
-      <c r="L2">
-        <f>I2/(J2/K2)</f>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>808</v>
-      </c>
-      <c r="B3" t="s">
-        <v>769</v>
       </c>
       <c r="C3" t="s">
         <v>764</v>
@@ -10667,38 +14510,31 @@
       <c r="D3" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>768</v>
+      <c r="E3" s="3" t="s">
+        <v>1047</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>282</v>
       </c>
       <c r="H3" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="I3">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="J3">
-        <v>0.25</v>
-      </c>
-      <c r="K3">
-        <v>0.03</v>
-      </c>
-      <c r="L3">
-        <f>I3/(J3/K3)</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="B4" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C4" t="s">
         <v>764</v>
@@ -10706,30 +14542,23 @@
       <c r="D4" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>770</v>
+      <c r="E4" s="3" t="s">
+        <v>1040</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>281</v>
       </c>
       <c r="H4" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="I4">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>0.06</v>
-      </c>
-      <c r="L4">
-        <f>I4/(J4/K4)</f>
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -10774,13 +14603,13 @@
         <v>11</v>
       </c>
       <c r="E1" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="F1" t="s">
         <v>761</v>
       </c>
       <c r="G1" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -10805,7 +14634,7 @@
         <v>763</v>
       </c>
       <c r="G2" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -10830,7 +14659,7 @@
         <v>763</v>
       </c>
       <c r="G3" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -10855,7 +14684,7 @@
         <v>763</v>
       </c>
       <c r="G4" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -10880,7 +14709,7 @@
         <v>763</v>
       </c>
       <c r="G5" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -10905,7 +14734,7 @@
         <v>763</v>
       </c>
       <c r="G6" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -10930,7 +14759,7 @@
         <v>763</v>
       </c>
       <c r="G7" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -10955,7 +14784,7 @@
         <v>763</v>
       </c>
       <c r="G8" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14" customHeight="1" x14ac:dyDescent="0.2">
@@ -10980,7 +14809,7 @@
         <v>763</v>
       </c>
       <c r="G9" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
@@ -11005,7 +14834,7 @@
         <v>763</v>
       </c>
       <c r="G10" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
@@ -11027,10 +14856,10 @@
         <v>her002</v>
       </c>
       <c r="F11" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G11" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
@@ -11052,10 +14881,10 @@
         <v>her002</v>
       </c>
       <c r="F12" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G12" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -11077,10 +14906,10 @@
         <v>her002</v>
       </c>
       <c r="F13" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G13" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
@@ -11102,10 +14931,10 @@
         <v>her002</v>
       </c>
       <c r="F14" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G14" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -11127,10 +14956,10 @@
         <v>her002</v>
       </c>
       <c r="F15" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G15" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
@@ -11152,10 +14981,10 @@
         <v>her002</v>
       </c>
       <c r="F16" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G16" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
@@ -11177,10 +15006,10 @@
         <v>her002</v>
       </c>
       <c r="F17" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G17" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
@@ -11202,10 +15031,10 @@
         <v>her002</v>
       </c>
       <c r="F18" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G18" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
@@ -11227,10 +15056,10 @@
         <v>her002</v>
       </c>
       <c r="F19" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G19" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
@@ -11252,10 +15081,10 @@
         <v>her002</v>
       </c>
       <c r="F20" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G20" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
@@ -11277,10 +15106,10 @@
         <v>her003</v>
       </c>
       <c r="F21" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G21" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
@@ -11302,10 +15131,10 @@
         <v>her003</v>
       </c>
       <c r="F22" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G22" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
@@ -11327,10 +15156,10 @@
         <v>her003</v>
       </c>
       <c r="F23" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G23" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
@@ -11352,10 +15181,10 @@
         <v>her003</v>
       </c>
       <c r="F24" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G24" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
@@ -11377,10 +15206,10 @@
         <v>her003</v>
       </c>
       <c r="F25" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G25" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -11402,10 +15231,10 @@
         <v>her003</v>
       </c>
       <c r="F26" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G26" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -11427,10 +15256,10 @@
         <v>her003</v>
       </c>
       <c r="F27" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G27" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
@@ -11452,10 +15281,10 @@
         <v>her003</v>
       </c>
       <c r="F28" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="G28" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
     </row>
   </sheetData>
@@ -11491,12 +15320,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57C794A-5FA1-4646-81AA-07F6C43DAC20}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="B1" t="s">
         <v>761</v>
@@ -11514,69 +15346,56 @@
         <v>760</v>
       </c>
       <c r="G1" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="H1" t="s">
-        <v>811</v>
+        <v>803</v>
       </c>
       <c r="I1" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="J1" t="s">
-        <v>848</v>
-      </c>
-      <c r="K1" t="s">
-        <v>847</v>
-      </c>
-      <c r="L1" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>812</v>
+        <v>804</v>
       </c>
       <c r="B2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C2" t="s">
         <v>764</v>
       </c>
       <c r="D2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="E2" t="s">
-        <v>776</v>
+        <v>972</v>
       </c>
       <c r="F2" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="H2" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="I2">
-        <v>650</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>0.1</v>
-      </c>
-      <c r="L2">
-        <f t="shared" ref="L2:L3" si="0">(20*I2)/J2</f>
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="B3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C3" t="s">
         <v>764</v>
@@ -11585,68 +15404,1356 @@
         <v>657</v>
       </c>
       <c r="E3" t="s">
-        <v>779</v>
+        <v>973</v>
       </c>
       <c r="F3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="H3" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="I3">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>0.3</v>
-      </c>
-      <c r="L3">
-        <f t="shared" si="0"/>
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="B4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C4" t="s">
         <v>764</v>
       </c>
       <c r="D4" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="E4" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="F4" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="H4" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="I4">
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B5" t="s">
+        <v>902</v>
+      </c>
+      <c r="C5" t="s">
+        <v>764</v>
+      </c>
+      <c r="D5" t="s">
+        <v>901</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="F5" t="s">
+        <v>956</v>
+      </c>
+      <c r="G5" t="s">
+        <v>903</v>
+      </c>
+      <c r="H5" t="s">
+        <v>831</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5">
         <v>40</v>
       </c>
-      <c r="J4">
-        <v>0.1</v>
-      </c>
-      <c r="K4">
-        <v>0.02</v>
-      </c>
-      <c r="L4">
-        <f>(20*I4)/J4</f>
-        <v>8000</v>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B6" t="s">
+        <v>999</v>
+      </c>
+      <c r="C6" t="s">
+        <v>764</v>
+      </c>
+      <c r="D6" t="s">
+        <v>998</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F6" t="s">
+        <v>773</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H6" t="s">
+        <v>830</v>
+      </c>
+      <c r="I6">
+        <v>1000</v>
+      </c>
+      <c r="J6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B7" t="s">
+        <v>906</v>
+      </c>
+      <c r="C7" t="s">
+        <v>948</v>
+      </c>
+      <c r="D7" t="s">
+        <v>906</v>
+      </c>
+      <c r="E7" t="s">
+        <v>958</v>
+      </c>
+      <c r="F7" t="s">
+        <v>765</v>
+      </c>
+      <c r="G7" t="s">
+        <v>907</v>
+      </c>
+      <c r="H7" t="s">
+        <v>832</v>
+      </c>
+      <c r="I7">
+        <v>1000</v>
+      </c>
+      <c r="J7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B8" t="s">
+        <v>910</v>
+      </c>
+      <c r="C8" t="s">
+        <v>948</v>
+      </c>
+      <c r="D8" t="s">
+        <v>910</v>
+      </c>
+      <c r="E8" t="s">
+        <v>960</v>
+      </c>
+      <c r="F8" t="s">
+        <v>773</v>
+      </c>
+      <c r="G8" t="s">
+        <v>911</v>
+      </c>
+      <c r="H8" t="s">
+        <v>832</v>
+      </c>
+      <c r="I8">
+        <v>1000</v>
+      </c>
+      <c r="J8">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B9" t="s">
+        <v>929</v>
+      </c>
+      <c r="C9" t="s">
+        <v>948</v>
+      </c>
+      <c r="D9" t="s">
+        <v>928</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="F9" t="s">
+        <v>789</v>
+      </c>
+      <c r="G9" t="s">
+        <v>919</v>
+      </c>
+      <c r="H9" t="s">
+        <v>832</v>
+      </c>
+      <c r="I9">
+        <v>100</v>
+      </c>
+      <c r="J9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B10" t="s">
+        <v>931</v>
+      </c>
+      <c r="C10" t="s">
+        <v>948</v>
+      </c>
+      <c r="D10" t="s">
+        <v>930</v>
+      </c>
+      <c r="E10" t="s">
+        <v>966</v>
+      </c>
+      <c r="F10" t="s">
+        <v>773</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+      <c r="H10" t="s">
+        <v>832</v>
+      </c>
+      <c r="I10">
+        <v>250</v>
+      </c>
+      <c r="J10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B11" t="s">
+        <v>936</v>
+      </c>
+      <c r="C11" t="s">
+        <v>948</v>
+      </c>
+      <c r="D11" t="s">
+        <v>936</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="F11" t="s">
+        <v>778</v>
+      </c>
+      <c r="G11" t="s">
+        <v>937</v>
+      </c>
+      <c r="H11" t="s">
+        <v>832</v>
+      </c>
+      <c r="I11">
+        <v>100</v>
+      </c>
+      <c r="J11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B12" t="s">
+        <v>989</v>
+      </c>
+      <c r="C12" t="s">
+        <v>948</v>
+      </c>
+      <c r="D12" t="s">
+        <v>989</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F12" t="s">
+        <v>765</v>
+      </c>
+      <c r="G12" t="s">
+        <v>990</v>
+      </c>
+      <c r="H12" t="s">
+        <v>832</v>
+      </c>
+      <c r="I12">
+        <v>1000</v>
+      </c>
+      <c r="J12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
+        <v>993</v>
+      </c>
+      <c r="C13" t="s">
+        <v>948</v>
+      </c>
+      <c r="D13" t="s">
+        <v>993</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F13" t="s">
+        <v>765</v>
+      </c>
+      <c r="G13">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>832</v>
+      </c>
+      <c r="I13">
+        <v>1000</v>
+      </c>
+      <c r="J13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B14" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C14" t="s">
+        <v>948</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F14" t="s">
+        <v>765</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H14" t="s">
+        <v>832</v>
+      </c>
+      <c r="I14">
+        <v>1000</v>
+      </c>
+      <c r="J14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B15" t="s">
+        <v>876</v>
+      </c>
+      <c r="C15" t="s">
+        <v>948</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="G15">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s">
+        <v>832</v>
+      </c>
+      <c r="I15">
+        <v>1000</v>
+      </c>
+      <c r="J15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="B16" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="F16" t="s">
+        <v>773</v>
+      </c>
+      <c r="G16">
+        <v>23</v>
+      </c>
+      <c r="H16" t="s">
+        <v>832</v>
+      </c>
+      <c r="I16">
+        <v>1000</v>
+      </c>
+      <c r="J16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B17" t="s">
+        <v>920</v>
+      </c>
+      <c r="C17" t="s">
+        <v>951</v>
+      </c>
+      <c r="D17" t="s">
+        <v>721</v>
+      </c>
+      <c r="E17" t="s">
+        <v>964</v>
+      </c>
+      <c r="F17" t="s">
+        <v>773</v>
+      </c>
+      <c r="G17" t="s">
+        <v>919</v>
+      </c>
+      <c r="H17" t="s">
+        <v>830</v>
+      </c>
+      <c r="I17">
+        <v>100</v>
+      </c>
+      <c r="J17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B18" t="s">
+        <v>924</v>
+      </c>
+      <c r="C18" t="s">
+        <v>951</v>
+      </c>
+      <c r="D18" t="s">
+        <v>923</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="F18" t="s">
+        <v>778</v>
+      </c>
+      <c r="G18" t="s">
+        <v>919</v>
+      </c>
+      <c r="H18" t="s">
+        <v>830</v>
+      </c>
+      <c r="I18">
+        <v>1000</v>
+      </c>
+      <c r="J18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B19" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D19" t="s">
+        <v>700</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="F19" t="s">
+        <v>773</v>
+      </c>
+      <c r="G19">
+        <v>23</v>
+      </c>
+      <c r="H19" t="s">
+        <v>832</v>
+      </c>
+      <c r="I19">
+        <v>500</v>
+      </c>
+      <c r="J19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>986</v>
+      </c>
+      <c r="C20" t="s">
+        <v>988</v>
+      </c>
+      <c r="D20" t="s">
+        <v>985</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F20" t="s">
+        <v>773</v>
+      </c>
+      <c r="G20" t="s">
+        <v>987</v>
+      </c>
+      <c r="H20" t="s">
+        <v>832</v>
+      </c>
+      <c r="I20">
+        <v>1000</v>
+      </c>
+      <c r="J20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B21" t="s">
+        <v>980</v>
+      </c>
+      <c r="C21" t="s">
+        <v>979</v>
+      </c>
+      <c r="D21" t="s">
+        <v>910</v>
+      </c>
+      <c r="E21" t="s">
+        <v>959</v>
+      </c>
+      <c r="F21" t="s">
+        <v>773</v>
+      </c>
+      <c r="G21" t="s">
+        <v>911</v>
+      </c>
+      <c r="H21" t="s">
+        <v>832</v>
+      </c>
+      <c r="I21">
+        <v>1000</v>
+      </c>
+      <c r="J21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B22" t="s">
+        <v>925</v>
+      </c>
+      <c r="C22" t="s">
+        <v>952</v>
+      </c>
+      <c r="D22" t="s">
+        <v>923</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="F22" t="s">
+        <v>778</v>
+      </c>
+      <c r="G22" t="s">
+        <v>919</v>
+      </c>
+      <c r="H22" t="s">
+        <v>832</v>
+      </c>
+      <c r="I22">
+        <v>1000</v>
+      </c>
+      <c r="J22">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B23" t="s">
+        <v>939</v>
+      </c>
+      <c r="C23" t="s">
+        <v>955</v>
+      </c>
+      <c r="D23" t="s">
+        <v>938</v>
+      </c>
+      <c r="E23" t="s">
+        <v>959</v>
+      </c>
+      <c r="F23" t="s">
+        <v>773</v>
+      </c>
+      <c r="G23" t="s">
+        <v>940</v>
+      </c>
+      <c r="H23" t="s">
+        <v>832</v>
+      </c>
+      <c r="I23">
+        <v>500</v>
+      </c>
+      <c r="J23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B24" t="s">
+        <v>939</v>
+      </c>
+      <c r="C24" t="s">
+        <v>955</v>
+      </c>
+      <c r="D24" t="s">
+        <v>938</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="F24" t="s">
+        <v>773</v>
+      </c>
+      <c r="G24" t="s">
+        <v>940</v>
+      </c>
+      <c r="H24" t="s">
+        <v>832</v>
+      </c>
+      <c r="I24">
+        <v>500</v>
+      </c>
+      <c r="J24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B25" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="F25" t="s">
+        <v>773</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H25" t="s">
+        <v>832</v>
+      </c>
+      <c r="I25">
+        <v>1000</v>
+      </c>
+      <c r="J25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B26" t="s">
+        <v>916</v>
+      </c>
+      <c r="C26" t="s">
+        <v>949</v>
+      </c>
+      <c r="D26" t="s">
+        <v>915</v>
+      </c>
+      <c r="E26" t="s">
+        <v>957</v>
+      </c>
+      <c r="F26" t="s">
+        <v>765</v>
+      </c>
+      <c r="G26" t="s">
+        <v>914</v>
+      </c>
+      <c r="H26" t="s">
+        <v>832</v>
+      </c>
+      <c r="I26">
+        <v>1000</v>
+      </c>
+      <c r="J26">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B27" t="s">
+        <v>933</v>
+      </c>
+      <c r="C27" t="s">
+        <v>954</v>
+      </c>
+      <c r="D27" t="s">
+        <v>932</v>
+      </c>
+      <c r="E27" t="s">
+        <v>966</v>
+      </c>
+      <c r="F27" t="s">
+        <v>773</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+      <c r="H27" t="s">
+        <v>830</v>
+      </c>
+      <c r="I27">
+        <v>250</v>
+      </c>
+      <c r="J27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>935</v>
+      </c>
+      <c r="C28" t="s">
+        <v>954</v>
+      </c>
+      <c r="D28" t="s">
+        <v>934</v>
+      </c>
+      <c r="E28" t="s">
+        <v>967</v>
+      </c>
+      <c r="F28" t="s">
+        <v>765</v>
+      </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
+      <c r="H28" t="s">
+        <v>832</v>
+      </c>
+      <c r="I28">
+        <v>1000</v>
+      </c>
+      <c r="J28">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B29" t="s">
+        <v>935</v>
+      </c>
+      <c r="C29" t="s">
+        <v>954</v>
+      </c>
+      <c r="D29" t="s">
+        <v>934</v>
+      </c>
+      <c r="E29" t="s">
+        <v>968</v>
+      </c>
+      <c r="F29" t="s">
+        <v>969</v>
+      </c>
+      <c r="G29">
+        <v>6</v>
+      </c>
+      <c r="H29" t="s">
+        <v>832</v>
+      </c>
+      <c r="I29">
+        <v>1000</v>
+      </c>
+      <c r="J29">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B30" t="s">
+        <v>982</v>
+      </c>
+      <c r="C30" t="s">
+        <v>949</v>
+      </c>
+      <c r="D30" t="s">
+        <v>981</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="F30" t="s">
+        <v>773</v>
+      </c>
+      <c r="G30" t="s">
+        <v>983</v>
+      </c>
+      <c r="H30" t="s">
+        <v>832</v>
+      </c>
+      <c r="I30">
+        <v>1000</v>
+      </c>
+      <c r="J30">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B31" t="s">
+        <v>991</v>
+      </c>
+      <c r="C31" t="s">
+        <v>949</v>
+      </c>
+      <c r="D31" t="s">
+        <v>989</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F31" t="s">
+        <v>789</v>
+      </c>
+      <c r="G31" t="s">
+        <v>990</v>
+      </c>
+      <c r="H31" t="s">
+        <v>831</v>
+      </c>
+      <c r="I31">
+        <v>1000</v>
+      </c>
+      <c r="J31">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B32" t="s">
+        <v>992</v>
+      </c>
+      <c r="C32" t="s">
+        <v>949</v>
+      </c>
+      <c r="D32" t="s">
+        <v>989</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F32" t="s">
+        <v>969</v>
+      </c>
+      <c r="G32" t="s">
+        <v>990</v>
+      </c>
+      <c r="H32" t="s">
+        <v>831</v>
+      </c>
+      <c r="I32">
+        <v>1000</v>
+      </c>
+      <c r="J32">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C33" t="s">
+        <v>949</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F33" t="s">
+        <v>773</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H33" t="s">
+        <v>832</v>
+      </c>
+      <c r="I33">
+        <v>250</v>
+      </c>
+      <c r="J33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C34" t="s">
+        <v>949</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F34" t="s">
+        <v>778</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H34" t="s">
+        <v>832</v>
+      </c>
+      <c r="I34">
+        <v>1000</v>
+      </c>
+      <c r="J34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>909</v>
+      </c>
+      <c r="C35" t="s">
+        <v>888</v>
+      </c>
+      <c r="D35" t="s">
+        <v>908</v>
+      </c>
+      <c r="E35" t="s">
+        <v>958</v>
+      </c>
+      <c r="F35" t="s">
+        <v>765</v>
+      </c>
+      <c r="G35" t="s">
+        <v>907</v>
+      </c>
+      <c r="H35" t="s">
+        <v>832</v>
+      </c>
+      <c r="I35">
+        <v>1000</v>
+      </c>
+      <c r="J35">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>944</v>
+      </c>
+      <c r="C36" t="s">
+        <v>888</v>
+      </c>
+      <c r="D36" t="s">
+        <v>943</v>
+      </c>
+      <c r="E36" t="s">
+        <v>961</v>
+      </c>
+      <c r="F36" t="s">
+        <v>970</v>
+      </c>
+      <c r="G36">
+        <v>30</v>
+      </c>
+      <c r="H36" t="s">
+        <v>830</v>
+      </c>
+      <c r="I36">
+        <v>500</v>
+      </c>
+      <c r="J36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F37" t="s">
+        <v>773</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H37" t="s">
+        <v>830</v>
+      </c>
+      <c r="I37">
+        <v>250</v>
+      </c>
+      <c r="J37">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B38" t="s">
+        <v>905</v>
+      </c>
+      <c r="C38" t="s">
+        <v>947</v>
+      </c>
+      <c r="D38" t="s">
+        <v>904</v>
+      </c>
+      <c r="E38" t="s">
+        <v>957</v>
+      </c>
+      <c r="F38" t="s">
+        <v>765</v>
+      </c>
+      <c r="G38" t="s">
+        <v>903</v>
+      </c>
+      <c r="H38" t="s">
+        <v>831</v>
+      </c>
+      <c r="I38">
+        <v>1000</v>
+      </c>
+      <c r="J38">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B39" t="s">
+        <v>913</v>
+      </c>
+      <c r="C39" t="s">
+        <v>947</v>
+      </c>
+      <c r="D39" t="s">
+        <v>912</v>
+      </c>
+      <c r="E39" t="s">
+        <v>961</v>
+      </c>
+      <c r="F39" t="s">
+        <v>765</v>
+      </c>
+      <c r="G39" t="s">
+        <v>914</v>
+      </c>
+      <c r="H39" t="s">
+        <v>831</v>
+      </c>
+      <c r="I39">
+        <v>1000</v>
+      </c>
+      <c r="J39">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B40" t="s">
+        <v>922</v>
+      </c>
+      <c r="C40" t="s">
+        <v>947</v>
+      </c>
+      <c r="D40" t="s">
+        <v>921</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="F40" t="s">
+        <v>965</v>
+      </c>
+      <c r="G40" t="s">
+        <v>919</v>
+      </c>
+      <c r="H40" t="s">
+        <v>831</v>
+      </c>
+      <c r="I40">
+        <v>100</v>
+      </c>
+      <c r="J40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B41" t="s">
+        <v>942</v>
+      </c>
+      <c r="C41" t="s">
+        <v>947</v>
+      </c>
+      <c r="D41" t="s">
+        <v>941</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="F41" t="s">
+        <v>778</v>
+      </c>
+      <c r="G41">
+        <v>29</v>
+      </c>
+      <c r="H41" t="s">
+        <v>832</v>
+      </c>
+      <c r="I41">
+        <v>250</v>
+      </c>
+      <c r="J41">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B42" t="s">
+        <v>984</v>
+      </c>
+      <c r="C42" t="s">
+        <v>947</v>
+      </c>
+      <c r="D42" t="s">
+        <v>981</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="F42" t="s">
+        <v>789</v>
+      </c>
+      <c r="G42" t="s">
+        <v>983</v>
+      </c>
+      <c r="H42" t="s">
+        <v>831</v>
+      </c>
+      <c r="I42">
+        <v>1000</v>
+      </c>
+      <c r="J42">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B43" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C43" t="s">
+        <v>947</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F43" t="s">
+        <v>765</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H43" t="s">
+        <v>830</v>
+      </c>
+      <c r="I43">
+        <v>1000</v>
+      </c>
+      <c r="J43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C44" t="s">
+        <v>947</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>957</v>
+      </c>
+      <c r="F44" t="s">
+        <v>773</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H44" t="s">
+        <v>832</v>
+      </c>
+      <c r="I44">
+        <v>1000</v>
+      </c>
+      <c r="J44">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B45" t="s">
+        <v>927</v>
+      </c>
+      <c r="C45" t="s">
+        <v>953</v>
+      </c>
+      <c r="D45" t="s">
+        <v>926</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="F45" t="s">
+        <v>956</v>
+      </c>
+      <c r="G45" t="s">
+        <v>919</v>
+      </c>
+      <c r="H45" t="s">
+        <v>831</v>
+      </c>
+      <c r="I45">
+        <v>100</v>
+      </c>
+      <c r="J45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B46" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="F46" t="s">
+        <v>789</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H46" t="s">
+        <v>832</v>
+      </c>
+      <c r="I46">
+        <v>500</v>
+      </c>
+      <c r="J46">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>995</v>
+      </c>
+      <c r="C47" t="s">
+        <v>997</v>
+      </c>
+      <c r="D47" t="s">
+        <v>994</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F47" t="s">
+        <v>773</v>
+      </c>
+      <c r="G47" t="s">
+        <v>996</v>
+      </c>
+      <c r="H47" t="s">
+        <v>832</v>
+      </c>
+      <c r="I47">
+        <v>1000</v>
+      </c>
+      <c r="J47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
+        <v>918</v>
+      </c>
+      <c r="C48" t="s">
+        <v>950</v>
+      </c>
+      <c r="D48" t="s">
+        <v>917</v>
+      </c>
+      <c r="E48" t="s">
+        <v>962</v>
+      </c>
+      <c r="F48" t="s">
+        <v>963</v>
+      </c>
+      <c r="G48" t="s">
+        <v>919</v>
+      </c>
+      <c r="H48" t="s">
+        <v>832</v>
+      </c>
+      <c r="I48">
+        <v>1000</v>
+      </c>
+      <c r="J48">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>946</v>
+      </c>
+      <c r="C49" t="s">
+        <v>950</v>
+      </c>
+      <c r="D49" t="s">
+        <v>945</v>
+      </c>
+      <c r="E49" t="s">
+        <v>971</v>
+      </c>
+      <c r="F49" t="s">
+        <v>773</v>
+      </c>
+      <c r="G49">
+        <v>34</v>
+      </c>
+      <c r="H49" t="s">
+        <v>830</v>
+      </c>
+      <c r="I49">
+        <v>250</v>
+      </c>
+      <c r="J49">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -11658,7 +16765,7 @@
           <x14:formula1>
             <xm:f>ref!$A$17:$A$19</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H4</xm:sqref>
+          <xm:sqref>H26:H49 H2:H25</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -11691,13 +16798,13 @@
         <v>8</v>
       </c>
       <c r="D1" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="E1" t="s">
         <v>761</v>
       </c>
       <c r="F1" t="s">
-        <v>854</v>
+        <v>844</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -11716,10 +16823,10 @@
         <v>ins001</v>
       </c>
       <c r="E2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="F2" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J2" s="1"/>
     </row>
@@ -11739,10 +16846,10 @@
         <v>ins001</v>
       </c>
       <c r="E3" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="F3" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J3" s="1"/>
     </row>
@@ -11762,10 +16869,10 @@
         <v>ins001</v>
       </c>
       <c r="E4" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="F4" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J4" s="1"/>
     </row>
@@ -11785,10 +16892,10 @@
         <v>ins001</v>
       </c>
       <c r="E5" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="F5" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J5" s="1"/>
     </row>
@@ -11808,10 +16915,10 @@
         <v>ins001</v>
       </c>
       <c r="E6" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="F6" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J6" s="1"/>
     </row>
@@ -11831,10 +16938,10 @@
         <v>ins002</v>
       </c>
       <c r="E7" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F7" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J7" s="1"/>
     </row>
@@ -11854,10 +16961,10 @@
         <v>ins002</v>
       </c>
       <c r="E8" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F8" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J8" s="1"/>
     </row>
@@ -11877,10 +16984,10 @@
         <v>ins002</v>
       </c>
       <c r="E9" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F9" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J9" s="1"/>
     </row>
@@ -11900,10 +17007,10 @@
         <v>ins002</v>
       </c>
       <c r="E10" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="F10" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -11923,10 +17030,10 @@
         <v>ins003</v>
       </c>
       <c r="E11" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F11" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J11" s="1"/>
     </row>
@@ -11946,10 +17053,10 @@
         <v>ins003</v>
       </c>
       <c r="E12" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F12" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J12" s="1"/>
     </row>
@@ -11969,10 +17076,10 @@
         <v>ins003</v>
       </c>
       <c r="E13" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F13" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J13" s="1"/>
     </row>
@@ -11992,10 +17099,10 @@
         <v>ins003</v>
       </c>
       <c r="E14" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F14" t="s">
-        <v>844</v>
+        <v>836</v>
       </c>
       <c r="J14" s="1"/>
     </row>
